--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE2"/>
+  <dimension ref="A1:BE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,7 @@
     <col width="26" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="49" max="49"/>
     <col width="17" customWidth="1" min="50" max="50"/>
-    <col width="16" customWidth="1" min="51" max="51"/>
+    <col width="34" customWidth="1" min="51" max="51"/>
     <col width="14" customWidth="1" min="52" max="52"/>
     <col width="23" customWidth="1" min="53" max="53"/>
     <col width="15" customWidth="1" min="54" max="54"/>
@@ -929,6 +929,348 @@
       <c r="BD2" s="1" t="inlineStr"/>
       <c r="BE2" s="1" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>kassbohrer-maxima-shtor-00116344</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+      <c r="G3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2022 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
+Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
+Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
+Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
+Документы в порядке.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.
+Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>3400000</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/09.jpg</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr"/>
+      <c r="T3" s="1" t="inlineStr"/>
+      <c r="U3" s="1" t="inlineStr"/>
+      <c r="V3" s="1" t="inlineStr"/>
+      <c r="W3" s="1" t="inlineStr"/>
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z3" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA3" s="1" t="inlineStr"/>
+      <c r="AB3" s="1" t="inlineStr">
+        <is>
+          <t>3400000</t>
+        </is>
+      </c>
+      <c r="AC3" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD3" s="1" t="inlineStr"/>
+      <c r="AE3" s="1" t="inlineStr"/>
+      <c r="AF3" s="1" t="inlineStr"/>
+      <c r="AG3" s="1" t="inlineStr"/>
+      <c r="AH3" s="1" t="inlineStr"/>
+      <c r="AI3" s="1" t="inlineStr"/>
+      <c r="AJ3" s="1" t="inlineStr"/>
+      <c r="AK3" s="1" t="inlineStr"/>
+      <c r="AL3" s="1" t="inlineStr"/>
+      <c r="AM3" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN3" s="1" t="inlineStr"/>
+      <c r="AO3" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP3" s="1" t="inlineStr">
+        <is>
+          <t>Kassbohrer</t>
+        </is>
+      </c>
+      <c r="AQ3" s="1" t="inlineStr">
+        <is>
+          <t>Maxima</t>
+        </is>
+      </c>
+      <c r="AR3" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS3" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT3" s="1" t="inlineStr"/>
+      <c r="AU3" s="1" t="inlineStr"/>
+      <c r="AV3" s="1" t="inlineStr">
+        <is>
+          <t>WKVDAF30300116344</t>
+        </is>
+      </c>
+      <c r="AW3" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="AX3" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY3" s="1" t="inlineStr">
+        <is>
+          <t>Зависимая, на продольных рычагах</t>
+        </is>
+      </c>
+      <c r="AZ3" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
+      <c r="BA3" s="1" t="inlineStr">
+        <is>
+          <t>28540</t>
+        </is>
+      </c>
+      <c r="BB3" s="1" t="inlineStr">
+        <is>
+          <t>16520</t>
+        </is>
+      </c>
+      <c r="BC3" s="1" t="inlineStr">
+        <is>
+          <t>110.6</t>
+        </is>
+      </c>
+      <c r="BD3" s="1" t="inlineStr"/>
+      <c r="BE3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>kassbohrer-maxima-shtor-00124397</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr"/>
+      <c r="F4" s="1" t="inlineStr"/>
+      <c r="G4" s="1" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
+Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
+Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
+Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
+Документы в порядке.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.
+Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>3950000</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr"/>
+      <c r="Q4" s="1" t="inlineStr"/>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/09.jpg</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr"/>
+      <c r="T4" s="1" t="inlineStr"/>
+      <c r="U4" s="1" t="inlineStr"/>
+      <c r="V4" s="1" t="inlineStr"/>
+      <c r="W4" s="1" t="inlineStr"/>
+      <c r="X4" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y4" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z4" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA4" s="1" t="inlineStr"/>
+      <c r="AB4" s="1" t="inlineStr">
+        <is>
+          <t>3950000</t>
+        </is>
+      </c>
+      <c r="AC4" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD4" s="1" t="inlineStr"/>
+      <c r="AE4" s="1" t="inlineStr"/>
+      <c r="AF4" s="1" t="inlineStr"/>
+      <c r="AG4" s="1" t="inlineStr"/>
+      <c r="AH4" s="1" t="inlineStr"/>
+      <c r="AI4" s="1" t="inlineStr"/>
+      <c r="AJ4" s="1" t="inlineStr"/>
+      <c r="AK4" s="1" t="inlineStr"/>
+      <c r="AL4" s="1" t="inlineStr"/>
+      <c r="AM4" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN4" s="1" t="inlineStr"/>
+      <c r="AO4" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP4" s="1" t="inlineStr">
+        <is>
+          <t>Kassbohrer</t>
+        </is>
+      </c>
+      <c r="AQ4" s="1" t="inlineStr">
+        <is>
+          <t>Maxima</t>
+        </is>
+      </c>
+      <c r="AR4" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS4" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT4" s="1" t="inlineStr"/>
+      <c r="AU4" s="1" t="inlineStr"/>
+      <c r="AV4" s="1" t="inlineStr">
+        <is>
+          <t>WKVDAF30300124397</t>
+        </is>
+      </c>
+      <c r="AW4" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX4" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY4" s="1" t="inlineStr">
+        <is>
+          <t>Зависимая, на продольных рычагах</t>
+        </is>
+      </c>
+      <c r="AZ4" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
+      <c r="BA4" s="1" t="inlineStr">
+        <is>
+          <t>28540</t>
+        </is>
+      </c>
+      <c r="BB4" s="1" t="inlineStr">
+        <is>
+          <t>16520</t>
+        </is>
+      </c>
+      <c r="BC4" s="1" t="inlineStr">
+        <is>
+          <t>110.6</t>
+        </is>
+      </c>
+      <c r="BD4" s="1" t="inlineStr"/>
+      <c r="BE4" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -890,7 +890,11 @@
       </c>
       <c r="AT2" s="1" t="inlineStr"/>
       <c r="AU2" s="1" t="inlineStr"/>
-      <c r="AV2" s="1" t="inlineStr"/>
+      <c r="AV2" s="1" t="inlineStr">
+        <is>
+          <t>WKVDAF10300124805</t>
+        </is>
+      </c>
       <c r="AW2" s="1" t="inlineStr">
         <is>
           <t>2023</t>
@@ -981,7 +985,7 @@
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/09.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr"/>
@@ -1152,7 +1156,7 @@
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/09.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/08.jpg</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -985,7 +985,7 @@
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/10.jpg</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE4"/>
+  <dimension ref="A1:BE5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1275,6 +1275,166 @@
       <c r="BD4" s="1" t="inlineStr"/>
       <c r="BE4" s="1" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr"/>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>steelbear-pl24l-ea653666</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr"/>
+      <c r="F5" s="1" t="inlineStr"/>
+      <c r="G5" s="1" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr"/>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
+Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
+Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
+Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
+Поставка под заказ, срок — уточняйте.</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>2970000</t>
+        </is>
+      </c>
+      <c r="P5" s="1" t="inlineStr"/>
+      <c r="Q5" s="1" t="inlineStr"/>
+      <c r="R5" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
+        </is>
+      </c>
+      <c r="S5" s="1" t="inlineStr"/>
+      <c r="T5" s="1" t="inlineStr"/>
+      <c r="U5" s="1" t="inlineStr"/>
+      <c r="V5" s="1" t="inlineStr"/>
+      <c r="W5" s="1" t="inlineStr"/>
+      <c r="X5" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y5" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z5" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA5" s="1" t="inlineStr"/>
+      <c r="AB5" s="1" t="inlineStr">
+        <is>
+          <t>2970000</t>
+        </is>
+      </c>
+      <c r="AC5" s="1" t="inlineStr">
+        <is>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD5" s="1" t="inlineStr"/>
+      <c r="AE5" s="1" t="inlineStr"/>
+      <c r="AF5" s="1" t="inlineStr"/>
+      <c r="AG5" s="1" t="inlineStr"/>
+      <c r="AH5" s="1" t="inlineStr"/>
+      <c r="AI5" s="1" t="inlineStr"/>
+      <c r="AJ5" s="1" t="inlineStr"/>
+      <c r="AK5" s="1" t="inlineStr"/>
+      <c r="AL5" s="1" t="inlineStr"/>
+      <c r="AM5" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN5" s="1" t="inlineStr"/>
+      <c r="AO5" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP5" s="1" t="inlineStr">
+        <is>
+          <t>Steelbear</t>
+        </is>
+      </c>
+      <c r="AQ5" s="1" t="inlineStr">
+        <is>
+          <t>PL-24L</t>
+        </is>
+      </c>
+      <c r="AR5" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS5" s="1" t="inlineStr">
+        <is>
+          <t>Сортиментовоз</t>
+        </is>
+      </c>
+      <c r="AT5" s="1" t="inlineStr"/>
+      <c r="AU5" s="1" t="inlineStr"/>
+      <c r="AV5" s="1" t="inlineStr"/>
+      <c r="AW5" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AX5" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY5" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ5" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
+      <c r="BA5" s="1" t="inlineStr">
+        <is>
+          <t>37100</t>
+        </is>
+      </c>
+      <c r="BB5" s="1" t="inlineStr">
+        <is>
+          <t>13620</t>
+        </is>
+      </c>
+      <c r="BC5" s="1" t="inlineStr"/>
+      <c r="BD5" s="1" t="inlineStr"/>
+      <c r="BE5" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -467,7 +467,7 @@
     <col width="26" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="49" max="49"/>
     <col width="17" customWidth="1" min="50" max="50"/>
-    <col width="34" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="51" max="51"/>
     <col width="14" customWidth="1" min="52" max="52"/>
     <col width="23" customWidth="1" min="53" max="53"/>
     <col width="15" customWidth="1" min="54" max="54"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AY3" s="1" t="inlineStr">
         <is>
-          <t>Зависимая, на продольных рычагах</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ3" s="1" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AY4" s="1" t="inlineStr">
         <is>
-          <t>Зависимая, на продольных рычагах</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ4" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -461,7 +461,7 @@
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="25" customWidth="1" min="45" max="45"/>
     <col width="11" customWidth="1" min="46" max="46"/>
     <col width="12" customWidth="1" min="47" max="47"/>
     <col width="26" customWidth="1" min="48" max="48"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="AS5" s="1" t="inlineStr">
         <is>
-          <t>Сортиментовоз</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT5" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE5"/>
+  <dimension ref="A1:BE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1285,7 +1285,7 @@
       <c r="C5" s="1" t="inlineStr"/>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-ea653666</t>
+          <t>kassbohrer-maxima-shtor-00124732</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
@@ -1302,12 +1302,15 @@
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
-Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
-6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
-Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
-Поставка под заказ, срок — уточняйте.</t>
+          <t>Полуприцеп шторный Kassbohrer, 2023 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска рессорная, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Масса снаряжённого 7 630 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 39 000 кг.
+Внутренние размеры 13 600×2 480×2 700 мм, объём кузова 92 м³. Высота ССУ 1150 мм.
+Боковая обшивка из фанеры, пол — ламинированная фанера 30 мм.
+Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
+Документы в порядке.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.
+Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
       <c r="N5" s="1" t="inlineStr">
@@ -1317,14 +1320,14 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>3390000</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/06.jpg</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr"/>
@@ -1350,12 +1353,12 @@
       <c r="AA5" s="1" t="inlineStr"/>
       <c r="AB5" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>3390000</t>
         </is>
       </c>
       <c r="AC5" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD5" s="1" t="inlineStr"/>
@@ -1380,12 +1383,12 @@
       </c>
       <c r="AP5" s="1" t="inlineStr">
         <is>
-          <t>Steelbear</t>
+          <t>Kassbohrer</t>
         </is>
       </c>
       <c r="AQ5" s="1" t="inlineStr">
         <is>
-          <t>PL-24L</t>
+          <t>Maxima</t>
         </is>
       </c>
       <c r="AR5" s="1" t="inlineStr">
@@ -1395,15 +1398,19 @@
       </c>
       <c r="AS5" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Шторный</t>
         </is>
       </c>
       <c r="AT5" s="1" t="inlineStr"/>
       <c r="AU5" s="1" t="inlineStr"/>
-      <c r="AV5" s="1" t="inlineStr"/>
+      <c r="AV5" s="1" t="inlineStr">
+        <is>
+          <t>WKVDAF30300124732</t>
+        </is>
+      </c>
       <c r="AW5" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX5" s="1" t="inlineStr">
@@ -1413,7 +1420,7 @@
       </c>
       <c r="AY5" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ5" s="1" t="inlineStr">
@@ -1423,17 +1430,181 @@
       </c>
       <c r="BA5" s="1" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="BB5" s="1" t="inlineStr">
         <is>
-          <t>13620</t>
-        </is>
-      </c>
-      <c r="BC5" s="1" t="inlineStr"/>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC5" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="BD5" s="1" t="inlineStr"/>
       <c r="BE5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>steelbear-pl24l-ea653666</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" s="1" t="inlineStr"/>
+      <c r="G6" s="1" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
+Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
+Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
+Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
+Поставка под заказ, срок — уточняйте.</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>2970000</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr"/>
+      <c r="Q6" s="1" t="inlineStr"/>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="inlineStr"/>
+      <c r="T6" s="1" t="inlineStr"/>
+      <c r="U6" s="1" t="inlineStr"/>
+      <c r="V6" s="1" t="inlineStr"/>
+      <c r="W6" s="1" t="inlineStr"/>
+      <c r="X6" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y6" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z6" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA6" s="1" t="inlineStr"/>
+      <c r="AB6" s="1" t="inlineStr">
+        <is>
+          <t>2970000</t>
+        </is>
+      </c>
+      <c r="AC6" s="1" t="inlineStr">
+        <is>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD6" s="1" t="inlineStr"/>
+      <c r="AE6" s="1" t="inlineStr"/>
+      <c r="AF6" s="1" t="inlineStr"/>
+      <c r="AG6" s="1" t="inlineStr"/>
+      <c r="AH6" s="1" t="inlineStr"/>
+      <c r="AI6" s="1" t="inlineStr"/>
+      <c r="AJ6" s="1" t="inlineStr"/>
+      <c r="AK6" s="1" t="inlineStr"/>
+      <c r="AL6" s="1" t="inlineStr"/>
+      <c r="AM6" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN6" s="1" t="inlineStr"/>
+      <c r="AO6" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP6" s="1" t="inlineStr">
+        <is>
+          <t>Steelbear</t>
+        </is>
+      </c>
+      <c r="AQ6" s="1" t="inlineStr">
+        <is>
+          <t>PL-24L</t>
+        </is>
+      </c>
+      <c r="AR6" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS6" s="1" t="inlineStr">
+        <is>
+          <t>Лесовоз (сортиментовоз)</t>
+        </is>
+      </c>
+      <c r="AT6" s="1" t="inlineStr"/>
+      <c r="AU6" s="1" t="inlineStr"/>
+      <c r="AV6" s="1" t="inlineStr"/>
+      <c r="AW6" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AX6" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY6" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ6" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
+      <c r="BA6" s="1" t="inlineStr">
+        <is>
+          <t>37100</t>
+        </is>
+      </c>
+      <c r="BB6" s="1" t="inlineStr">
+        <is>
+          <t>13620</t>
+        </is>
+      </c>
+      <c r="BC6" s="1" t="inlineStr"/>
+      <c r="BD6" s="1" t="inlineStr"/>
+      <c r="BE6" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>3400000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
       <c r="AA3" s="1" t="inlineStr"/>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>3400000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>3950000</t>
+          <t>3290000</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
       <c r="AA4" s="1" t="inlineStr"/>
       <c r="AB4" s="1" t="inlineStr">
         <is>
-          <t>3950000</t>
+          <t>3290000</t>
         </is>
       </c>
       <c r="AC4" s="1" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>3390000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -1353,7 +1353,7 @@
       <c r="AA5" s="1" t="inlineStr"/>
       <c r="AB5" s="1" t="inlineStr">
         <is>
-          <t>3390000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC5" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE6"/>
+  <dimension ref="A1:BE7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1606,6 +1606,173 @@
       <c r="BD6" s="1" t="inlineStr"/>
       <c r="BE6" s="1" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>v-trailer-329d-r0000119</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — собственная сварная конструкция, усиленная рама с дополнительными рёбрами жёсткости на скручивание. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+VIN XZFVKRP3DR0000119.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="inlineStr"/>
+      <c r="Q7" s="1" t="inlineStr"/>
+      <c r="R7" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+        </is>
+      </c>
+      <c r="S7" s="1" t="inlineStr"/>
+      <c r="T7" s="1" t="inlineStr"/>
+      <c r="U7" s="1" t="inlineStr"/>
+      <c r="V7" s="1" t="inlineStr"/>
+      <c r="W7" s="1" t="inlineStr"/>
+      <c r="X7" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y7" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z7" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA7" s="1" t="inlineStr"/>
+      <c r="AB7" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="AC7" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD7" s="1" t="inlineStr"/>
+      <c r="AE7" s="1" t="inlineStr"/>
+      <c r="AF7" s="1" t="inlineStr"/>
+      <c r="AG7" s="1" t="inlineStr"/>
+      <c r="AH7" s="1" t="inlineStr"/>
+      <c r="AI7" s="1" t="inlineStr"/>
+      <c r="AJ7" s="1" t="inlineStr"/>
+      <c r="AK7" s="1" t="inlineStr"/>
+      <c r="AL7" s="1" t="inlineStr"/>
+      <c r="AM7" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN7" s="1" t="inlineStr"/>
+      <c r="AO7" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP7" s="1" t="inlineStr">
+        <is>
+          <t>V-Trailer</t>
+        </is>
+      </c>
+      <c r="AQ7" s="1" t="inlineStr">
+        <is>
+          <t>329D</t>
+        </is>
+      </c>
+      <c r="AR7" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS7" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT7" s="1" t="inlineStr"/>
+      <c r="AU7" s="1" t="inlineStr"/>
+      <c r="AV7" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
+      <c r="AW7" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX7" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY7" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ7" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA7" s="1" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB7" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC7" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="BD7" s="1" t="inlineStr"/>
+      <c r="BE7" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -1634,7 +1634,7 @@
       <c r="M7" s="1" t="inlineStr">
         <is>
           <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — собственная сварная конструкция, усиленная рама с дополнительными рёбрами жёсткости на скручивание. По бортам — корзины под коники, по 7 штук на сторону.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
 13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
 VIN XZFVKRP3DR0000119.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE7"/>
+  <dimension ref="A1:BE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,7 @@
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="25" customWidth="1" min="45" max="45"/>
@@ -773,7 +773,7 @@
       <c r="C2" s="1" t="inlineStr"/>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-iso-xx246877</t>
+          <t>interpricep-853375-r0000773</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -790,14 +790,12 @@
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп изотермический Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска пневматическая, тормоза барабанные.
-Грузоподъёмность 31 290 кг.
-Длина кузова 13,7 м, объём 94 м³.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Возможна аренда — уточняйте условия по телефону.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
+          <t>Полуприцеп-контейнеровоз ИнтерПрицеп 853375, 2024 год, в работе, полностью исправен.
+4 оси (3 + выносная балансирная), тормоза дисковые, ABS SORL. Подвеска пневматическая, с функцией подъёма осей — меньше износ резины на порожняке и разворотах. Шины 385/55R22.5, комплект 8+1 запасное.
+Берёт контейнеры 20', 30', 40' и High Cube — под большинство стандартных грузоперевозок без переоборудования. Разрешённая максимальная масса 47 000 кг, грузоподъёмность 41 000 кг. Высота погрузки 1 100 мм.
+Инструментальный ящик Daken, полный комплект пневморазводки и ЭБС.
+VIN EAR853375R0000773.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
@@ -807,14 +805,14 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>4850000</t>
+          <t>1390000</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/09.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/06.jpg</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr"/>
@@ -840,7 +838,7 @@
       <c r="AA2" s="1" t="inlineStr"/>
       <c r="AB2" s="1" t="inlineStr">
         <is>
-          <t>4850000</t>
+          <t>1390000</t>
         </is>
       </c>
       <c r="AC2" s="1" t="inlineStr">
@@ -870,12 +868,12 @@
       </c>
       <c r="AP2" s="1" t="inlineStr">
         <is>
-          <t>Kassbohrer</t>
+          <t>ИнтерПрицеп</t>
         </is>
       </c>
       <c r="AQ2" s="1" t="inlineStr">
         <is>
-          <t>Maxima</t>
+          <t>853375</t>
         </is>
       </c>
       <c r="AR2" s="1" t="inlineStr">
@@ -885,24 +883,24 @@
       </c>
       <c r="AS2" s="1" t="inlineStr">
         <is>
-          <t>Изотермический</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT2" s="1" t="inlineStr"/>
       <c r="AU2" s="1" t="inlineStr"/>
       <c r="AV2" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF10300124805</t>
+          <t>EAR853375R0000773</t>
         </is>
       </c>
       <c r="AW2" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX2" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY2" s="1" t="inlineStr">
@@ -912,24 +910,20 @@
       </c>
       <c r="AZ2" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA2" s="1" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="BB2" s="1" t="inlineStr">
         <is>
-          <t>13700</t>
-        </is>
-      </c>
-      <c r="BC2" s="1" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="BC2" s="1" t="inlineStr"/>
       <c r="BD2" s="1" t="inlineStr"/>
       <c r="BE2" s="1" t="inlineStr"/>
     </row>
@@ -943,7 +937,7 @@
       <c r="C3" s="1" t="inlineStr"/>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-shtor-00116344</t>
+          <t>kassbohrer-maxima-iso-xx246877</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr"/>
@@ -960,14 +954,13 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer Maxima, 2022 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
-Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
-Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
-Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
+          <t>Полуприцеп изотермический Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска пневматическая, тормоза барабанные.
+Грузоподъёмность 31 290 кг.
+Длина кузова 13,7 м, объём 94 м³.
 Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
 Документы в порядке.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.
+Возможна аренда — уточняйте условия по телефону.
 Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
@@ -978,14 +971,14 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>4850000</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/09.jpg</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr"/>
@@ -1011,7 +1004,7 @@
       <c r="AA3" s="1" t="inlineStr"/>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>4850000</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
@@ -1056,19 +1049,19 @@
       </c>
       <c r="AS3" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Изотермический</t>
         </is>
       </c>
       <c r="AT3" s="1" t="inlineStr"/>
       <c r="AU3" s="1" t="inlineStr"/>
       <c r="AV3" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF30300116344</t>
+          <t>WKVDAF10300124805</t>
         </is>
       </c>
       <c r="AW3" s="1" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX3" s="1" t="inlineStr">
@@ -1078,7 +1071,7 @@
       </c>
       <c r="AY3" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ3" s="1" t="inlineStr">
@@ -1088,17 +1081,17 @@
       </c>
       <c r="BA3" s="1" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="BB3" s="1" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="BC3" s="1" t="inlineStr">
         <is>
-          <t>110.6</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BD3" s="1" t="inlineStr"/>
@@ -1114,7 +1107,7 @@
       <c r="C4" s="1" t="inlineStr"/>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-shtor-00124397</t>
+          <t>kassbohrer-maxima-shtor-00116344</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
@@ -1131,7 +1124,7 @@
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2022 год выпуска, TIR-исполнение.
 Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
 Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
 Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
@@ -1149,14 +1142,14 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>3290000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/10.jpg</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>
@@ -1182,7 +1175,7 @@
       <c r="AA4" s="1" t="inlineStr"/>
       <c r="AB4" s="1" t="inlineStr">
         <is>
-          <t>3290000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC4" s="1" t="inlineStr">
@@ -1234,12 +1227,12 @@
       <c r="AU4" s="1" t="inlineStr"/>
       <c r="AV4" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF30300124397</t>
+          <t>WKVDAF30300116344</t>
         </is>
       </c>
       <c r="AW4" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="AX4" s="1" t="inlineStr">
@@ -1285,7 +1278,7 @@
       <c r="C5" s="1" t="inlineStr"/>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-shtor-00124732</t>
+          <t>kassbohrer-maxima-shtor-00124397</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
@@ -1302,11 +1295,11 @@
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска рессорная, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
-Масса снаряжённого 7 630 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 39 000 кг.
-Внутренние размеры 13 600×2 480×2 700 мм, объём кузова 92 м³. Высота ССУ 1150 мм.
-Боковая обшивка из фанеры, пол — ламинированная фанера 30 мм.
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
+Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
+Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
 Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
 Документы в порядке.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.
@@ -1320,14 +1313,14 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>3290000</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/08.jpg</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr"/>
@@ -1353,7 +1346,7 @@
       <c r="AA5" s="1" t="inlineStr"/>
       <c r="AB5" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>3290000</t>
         </is>
       </c>
       <c r="AC5" s="1" t="inlineStr">
@@ -1405,7 +1398,7 @@
       <c r="AU5" s="1" t="inlineStr"/>
       <c r="AV5" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF30300124732</t>
+          <t>WKVDAF30300124397</t>
         </is>
       </c>
       <c r="AW5" s="1" t="inlineStr">
@@ -1435,12 +1428,12 @@
       </c>
       <c r="BB5" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="BC5" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>110.6</t>
         </is>
       </c>
       <c r="BD5" s="1" t="inlineStr"/>
@@ -1456,7 +1449,7 @@
       <c r="C6" s="1" t="inlineStr"/>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-ea653666</t>
+          <t>kassbohrer-maxima-shtor-00124732</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -1473,12 +1466,15 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
-Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
-6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
-Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
-Поставка под заказ, срок — уточняйте.</t>
+          <t>Полуприцеп шторный Kassbohrer, 2023 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска рессорная, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Масса снаряжённого 7 630 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 39 000 кг.
+Внутренние размеры 13 600×2 480×2 700 мм, объём кузова 92 м³. Высота ССУ 1150 мм.
+Боковая обшивка из фанеры, пол — ламинированная фанера 30 мм.
+Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
+Документы в порядке.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.
+Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr">
@@ -1488,14 +1484,14 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/06.jpg</t>
         </is>
       </c>
       <c r="S6" s="1" t="inlineStr"/>
@@ -1521,12 +1517,12 @@
       <c r="AA6" s="1" t="inlineStr"/>
       <c r="AB6" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC6" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD6" s="1" t="inlineStr"/>
@@ -1551,12 +1547,12 @@
       </c>
       <c r="AP6" s="1" t="inlineStr">
         <is>
-          <t>Steelbear</t>
+          <t>Kassbohrer</t>
         </is>
       </c>
       <c r="AQ6" s="1" t="inlineStr">
         <is>
-          <t>PL-24L</t>
+          <t>Maxima</t>
         </is>
       </c>
       <c r="AR6" s="1" t="inlineStr">
@@ -1566,15 +1562,19 @@
       </c>
       <c r="AS6" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Шторный</t>
         </is>
       </c>
       <c r="AT6" s="1" t="inlineStr"/>
       <c r="AU6" s="1" t="inlineStr"/>
-      <c r="AV6" s="1" t="inlineStr"/>
+      <c r="AV6" s="1" t="inlineStr">
+        <is>
+          <t>WKVDAF30300124732</t>
+        </is>
+      </c>
       <c r="AW6" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX6" s="1" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AY6" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ6" s="1" t="inlineStr">
@@ -1594,15 +1594,19 @@
       </c>
       <c r="BA6" s="1" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="BB6" s="1" t="inlineStr">
         <is>
-          <t>13620</t>
-        </is>
-      </c>
-      <c r="BC6" s="1" t="inlineStr"/>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC6" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="BD6" s="1" t="inlineStr"/>
       <c r="BE6" s="1" t="inlineStr"/>
     </row>
@@ -1616,7 +1620,7 @@
       <c r="C7" s="1" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>v-trailer-329d-r0000119</t>
+          <t>steelbear-pl24l-ea653666</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -1633,11 +1637,12 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-VIN XZFVKRP3DR0000119.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
+Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
+Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
+Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
+Поставка под заказ, срок — уточняйте.</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
@@ -1647,14 +1652,14 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
         </is>
       </c>
       <c r="S7" s="1" t="inlineStr"/>
@@ -1680,12 +1685,12 @@
       <c r="AA7" s="1" t="inlineStr"/>
       <c r="AB7" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD7" s="1" t="inlineStr"/>
@@ -1710,12 +1715,12 @@
       </c>
       <c r="AP7" s="1" t="inlineStr">
         <is>
-          <t>V-Trailer</t>
+          <t>Steelbear</t>
         </is>
       </c>
       <c r="AQ7" s="1" t="inlineStr">
         <is>
-          <t>329D</t>
+          <t>PL-24L</t>
         </is>
       </c>
       <c r="AR7" s="1" t="inlineStr">
@@ -1725,19 +1730,15 @@
       </c>
       <c r="AS7" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT7" s="1" t="inlineStr"/>
       <c r="AU7" s="1" t="inlineStr"/>
-      <c r="AV7" s="1" t="inlineStr">
-        <is>
-          <t>XZFVKRP3DR0000119</t>
-        </is>
-      </c>
+      <c r="AV7" s="1" t="inlineStr"/>
       <c r="AW7" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX7" s="1" t="inlineStr">
@@ -1752,26 +1753,189 @@
       </c>
       <c r="AZ7" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA7" s="1" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="BB7" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC7" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
+          <t>13620</t>
+        </is>
+      </c>
+      <c r="BC7" s="1" t="inlineStr"/>
       <c r="BD7" s="1" t="inlineStr"/>
       <c r="BE7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>v-trailer-329d-r0000119</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr"/>
+      <c r="G8" s="1" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr"/>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+VIN XZFVKRP3DR0000119.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="inlineStr"/>
+      <c r="Q8" s="1" t="inlineStr"/>
+      <c r="R8" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+        </is>
+      </c>
+      <c r="S8" s="1" t="inlineStr"/>
+      <c r="T8" s="1" t="inlineStr"/>
+      <c r="U8" s="1" t="inlineStr"/>
+      <c r="V8" s="1" t="inlineStr"/>
+      <c r="W8" s="1" t="inlineStr"/>
+      <c r="X8" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y8" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z8" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA8" s="1" t="inlineStr"/>
+      <c r="AB8" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="AC8" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD8" s="1" t="inlineStr"/>
+      <c r="AE8" s="1" t="inlineStr"/>
+      <c r="AF8" s="1" t="inlineStr"/>
+      <c r="AG8" s="1" t="inlineStr"/>
+      <c r="AH8" s="1" t="inlineStr"/>
+      <c r="AI8" s="1" t="inlineStr"/>
+      <c r="AJ8" s="1" t="inlineStr"/>
+      <c r="AK8" s="1" t="inlineStr"/>
+      <c r="AL8" s="1" t="inlineStr"/>
+      <c r="AM8" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN8" s="1" t="inlineStr"/>
+      <c r="AO8" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP8" s="1" t="inlineStr">
+        <is>
+          <t>V-Trailer</t>
+        </is>
+      </c>
+      <c r="AQ8" s="1" t="inlineStr">
+        <is>
+          <t>329D</t>
+        </is>
+      </c>
+      <c r="AR8" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS8" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT8" s="1" t="inlineStr"/>
+      <c r="AU8" s="1" t="inlineStr"/>
+      <c r="AV8" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
+      <c r="AW8" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX8" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY8" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ8" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA8" s="1" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB8" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC8" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="BD8" s="1" t="inlineStr"/>
+      <c r="BE8" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE8"/>
+  <dimension ref="A1:BE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -459,7 +459,7 @@
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="25" customWidth="1" min="45" max="45"/>
     <col width="11" customWidth="1" min="46" max="46"/>
@@ -1780,7 +1780,7 @@
       <c r="C8" s="1" t="inlineStr"/>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>v-trailer-329d-r0000119</t>
+          <t>tonar-k4u-p0002033</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-VIN XZFVKRP3DR0000119.
+          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
+4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
+Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
+VIN X0T998910P0002033.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
@@ -1811,14 +1811,14 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
         </is>
       </c>
       <c r="S8" s="1" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
       <c r="AA8" s="1" t="inlineStr"/>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="AP8" s="1" t="inlineStr">
         <is>
-          <t>V-Trailer</t>
+          <t>Тонар</t>
         </is>
       </c>
       <c r="AQ8" s="1" t="inlineStr">
         <is>
-          <t>329D</t>
+          <t>K4-U (99891)</t>
         </is>
       </c>
       <c r="AR8" s="1" t="inlineStr">
@@ -1889,14 +1889,14 @@
       </c>
       <c r="AS8" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT8" s="1" t="inlineStr"/>
       <c r="AU8" s="1" t="inlineStr"/>
       <c r="AV8" s="1" t="inlineStr">
         <is>
-          <t>XZFVKRP3DR0000119</t>
+          <t>X0T998910P0002033</t>
         </is>
       </c>
       <c r="AW8" s="1" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="AX8" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY8" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ8" s="1" t="inlineStr">
@@ -1921,21 +1921,184 @@
       </c>
       <c r="BA8" s="1" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="BB8" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC8" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="BC8" s="1" t="inlineStr"/>
       <c r="BD8" s="1" t="inlineStr"/>
       <c r="BE8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr"/>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>v-trailer-329d-r0000119</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr"/>
+      <c r="F9" s="1" t="inlineStr"/>
+      <c r="G9" s="1" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr"/>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+VIN XZFVKRP3DR0000119.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="P9" s="1" t="inlineStr"/>
+      <c r="Q9" s="1" t="inlineStr"/>
+      <c r="R9" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+        </is>
+      </c>
+      <c r="S9" s="1" t="inlineStr"/>
+      <c r="T9" s="1" t="inlineStr"/>
+      <c r="U9" s="1" t="inlineStr"/>
+      <c r="V9" s="1" t="inlineStr"/>
+      <c r="W9" s="1" t="inlineStr"/>
+      <c r="X9" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y9" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z9" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA9" s="1" t="inlineStr"/>
+      <c r="AB9" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="AC9" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD9" s="1" t="inlineStr"/>
+      <c r="AE9" s="1" t="inlineStr"/>
+      <c r="AF9" s="1" t="inlineStr"/>
+      <c r="AG9" s="1" t="inlineStr"/>
+      <c r="AH9" s="1" t="inlineStr"/>
+      <c r="AI9" s="1" t="inlineStr"/>
+      <c r="AJ9" s="1" t="inlineStr"/>
+      <c r="AK9" s="1" t="inlineStr"/>
+      <c r="AL9" s="1" t="inlineStr"/>
+      <c r="AM9" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN9" s="1" t="inlineStr"/>
+      <c r="AO9" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP9" s="1" t="inlineStr">
+        <is>
+          <t>V-Trailer</t>
+        </is>
+      </c>
+      <c r="AQ9" s="1" t="inlineStr">
+        <is>
+          <t>329D</t>
+        </is>
+      </c>
+      <c r="AR9" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS9" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT9" s="1" t="inlineStr"/>
+      <c r="AU9" s="1" t="inlineStr"/>
+      <c r="AV9" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
+      <c r="AW9" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX9" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY9" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ9" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA9" s="1" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB9" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC9" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="BD9" s="1" t="inlineStr"/>
+      <c r="BE9" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AQ9" s="1" t="inlineStr">
         <is>
-          <t>329D</t>
+          <t>329</t>
         </is>
       </c>
       <c r="AR9" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -1125,7 +1125,7 @@
       <c r="M4" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп шторный Kassbohrer Maxima, 2022 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
 Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
 Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
 Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
@@ -1149,7 +1149,7 @@
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AZ4" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA4" s="1" t="inlineStr">
@@ -1296,7 +1296,7 @@
       <c r="M5" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп шторный Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
 Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
 Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
 Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
@@ -1320,7 +1320,7 @@
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/04.jpg</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AZ5" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA5" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE9"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1620,7 +1620,7 @@
       <c r="C7" s="1" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-ea653666</t>
+          <t>steelbear-pf41n-v000319</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
-Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
-6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
-Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
-Поставка под заказ, срок — уточняйте.</t>
+          <t>Полуприцеп-контейнеровоз Steelbear PF-41N (коммерческое название PF-41N FOX INTRA DISK), 4-х осный, универсал, под заказ.
+Перевозит 1×40-футовый контейнер (в т.ч. HQ), 2×20-футовых контейнера или 1×20-футовый по центру. Максимальная полная масса 47 000 кг, грузоподъёмность 41 100 кг, длина 12 600 мм.
+Осевой агрегат FOX B9-22S с дисковыми тормозами, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска FOX INTRA с подъёмом/опусканием 1-й оси (ручное управление) и 2-й оси (автоматическое). Электронная тормозная система Haldex EBS 4S/2M с функцией противоопрокидывания (RSS), информационная система INFOCENTER.
+Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая защита, заднее защитное устройство. Два инструментальных ящика SKARB с замком. Шины TYREX 385/55R22,5 на дисках KRONPRINZ, 9 колёс в комплекте (включая запасное).
+При покупке в лизинг — скидка от Минпромторга 10%.
+Заводская гарантия — 12 месяцев. Поставка — 10 рабочих дней с момента предоплаты.</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>3250000</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/15.jpg</t>
         </is>
       </c>
       <c r="S7" s="1" t="inlineStr"/>
@@ -1685,7 +1685,7 @@
       <c r="AA7" s="1" t="inlineStr"/>
       <c r="AB7" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>3250000</t>
         </is>
       </c>
       <c r="AC7" s="1" t="inlineStr">
@@ -1693,7 +1693,11 @@
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD7" s="1" t="inlineStr"/>
+      <c r="AD7" s="1" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
       <c r="AE7" s="1" t="inlineStr"/>
       <c r="AF7" s="1" t="inlineStr"/>
       <c r="AG7" s="1" t="inlineStr"/>
@@ -1704,7 +1708,7 @@
       <c r="AL7" s="1" t="inlineStr"/>
       <c r="AM7" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN7" s="1" t="inlineStr"/>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="AQ7" s="1" t="inlineStr">
         <is>
-          <t>PL-24L</t>
+          <t>PF-41N</t>
         </is>
       </c>
       <c r="AR7" s="1" t="inlineStr">
@@ -1730,7 +1734,7 @@
       </c>
       <c r="AS7" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT7" s="1" t="inlineStr"/>
@@ -1738,12 +1742,12 @@
       <c r="AV7" s="1" t="inlineStr"/>
       <c r="AW7" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX7" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY7" s="1" t="inlineStr">
@@ -1753,17 +1757,17 @@
       </c>
       <c r="AZ7" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA7" s="1" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>41100</t>
         </is>
       </c>
       <c r="BB7" s="1" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="BC7" s="1" t="inlineStr"/>
@@ -1780,7 +1784,7 @@
       <c r="C8" s="1" t="inlineStr"/>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>tonar-k4u-p0002033</t>
+          <t>steelbear-pl24l-ea653666</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -1797,11 +1801,12 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
-VIN X0T998910P0002033.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
+Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
+Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
+Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
+Поставка под заказ, срок — уточняйте.</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
@@ -1811,14 +1816,14 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
         </is>
       </c>
       <c r="S8" s="1" t="inlineStr"/>
@@ -1844,12 +1849,12 @@
       <c r="AA8" s="1" t="inlineStr"/>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD8" s="1" t="inlineStr"/>
@@ -1863,7 +1868,7 @@
       <c r="AL8" s="1" t="inlineStr"/>
       <c r="AM8" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN8" s="1" t="inlineStr"/>
@@ -1874,12 +1879,12 @@
       </c>
       <c r="AP8" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>Steelbear</t>
         </is>
       </c>
       <c r="AQ8" s="1" t="inlineStr">
         <is>
-          <t>K4-U (99891)</t>
+          <t>PL-24L</t>
         </is>
       </c>
       <c r="AR8" s="1" t="inlineStr">
@@ -1889,44 +1894,40 @@
       </c>
       <c r="AS8" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT8" s="1" t="inlineStr"/>
       <c r="AU8" s="1" t="inlineStr"/>
-      <c r="AV8" s="1" t="inlineStr">
-        <is>
-          <t>X0T998910P0002033</t>
-        </is>
-      </c>
+      <c r="AV8" s="1" t="inlineStr"/>
       <c r="AW8" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX8" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY8" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ8" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA8" s="1" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="BB8" s="1" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="BC8" s="1" t="inlineStr"/>
@@ -1943,7 +1944,7 @@
       <c r="C9" s="1" t="inlineStr"/>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>v-trailer-329d-r0000119</t>
+          <t>tonar-k4u-p0002033</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -1960,10 +1961,10 @@
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-VIN XZFVKRP3DR0000119.
+          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
+4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
+Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
+VIN X0T998910P0002033.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
@@ -1974,14 +1975,14 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr"/>
@@ -2007,7 +2008,7 @@
       <c r="AA9" s="1" t="inlineStr"/>
       <c r="AB9" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
@@ -2037,12 +2038,12 @@
       </c>
       <c r="AP9" s="1" t="inlineStr">
         <is>
-          <t>V-Trailer</t>
+          <t>Тонар</t>
         </is>
       </c>
       <c r="AQ9" s="1" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>K4-U (99891)</t>
         </is>
       </c>
       <c r="AR9" s="1" t="inlineStr">
@@ -2052,14 +2053,14 @@
       </c>
       <c r="AS9" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT9" s="1" t="inlineStr"/>
       <c r="AU9" s="1" t="inlineStr"/>
       <c r="AV9" s="1" t="inlineStr">
         <is>
-          <t>XZFVKRP3DR0000119</t>
+          <t>X0T998910P0002033</t>
         </is>
       </c>
       <c r="AW9" s="1" t="inlineStr">
@@ -2069,12 +2070,12 @@
       </c>
       <c r="AX9" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY9" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ9" s="1" t="inlineStr">
@@ -2084,21 +2085,184 @@
       </c>
       <c r="BA9" s="1" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="BB9" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC9" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="BC9" s="1" t="inlineStr"/>
       <c r="BD9" s="1" t="inlineStr"/>
       <c r="BE9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr"/>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>v-trailer-329d-r0000119</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr"/>
+      <c r="F10" s="1" t="inlineStr"/>
+      <c r="G10" s="1" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+VIN XZFVKRP3DR0000119.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="P10" s="1" t="inlineStr"/>
+      <c r="Q10" s="1" t="inlineStr"/>
+      <c r="R10" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+        </is>
+      </c>
+      <c r="S10" s="1" t="inlineStr"/>
+      <c r="T10" s="1" t="inlineStr"/>
+      <c r="U10" s="1" t="inlineStr"/>
+      <c r="V10" s="1" t="inlineStr"/>
+      <c r="W10" s="1" t="inlineStr"/>
+      <c r="X10" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y10" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z10" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA10" s="1" t="inlineStr"/>
+      <c r="AB10" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="AC10" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD10" s="1" t="inlineStr"/>
+      <c r="AE10" s="1" t="inlineStr"/>
+      <c r="AF10" s="1" t="inlineStr"/>
+      <c r="AG10" s="1" t="inlineStr"/>
+      <c r="AH10" s="1" t="inlineStr"/>
+      <c r="AI10" s="1" t="inlineStr"/>
+      <c r="AJ10" s="1" t="inlineStr"/>
+      <c r="AK10" s="1" t="inlineStr"/>
+      <c r="AL10" s="1" t="inlineStr"/>
+      <c r="AM10" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN10" s="1" t="inlineStr"/>
+      <c r="AO10" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP10" s="1" t="inlineStr">
+        <is>
+          <t>V-Trailer</t>
+        </is>
+      </c>
+      <c r="AQ10" s="1" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AR10" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS10" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT10" s="1" t="inlineStr"/>
+      <c r="AU10" s="1" t="inlineStr"/>
+      <c r="AV10" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
+      <c r="AW10" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX10" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY10" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ10" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA10" s="1" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB10" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC10" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="BD10" s="1" t="inlineStr"/>
+      <c r="BE10" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1784,7 +1784,7 @@
       <c r="C8" s="1" t="inlineStr"/>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-ea653666</t>
+          <t>steelbear-pl24l-avg36</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -1801,12 +1801,13 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
-Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
-6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
-Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
-Поставка под заказ, срок — уточняйте.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L AVG), 3-х осный, под заказ.
+Осевой агрегат AVG Axle, квадратная ось сечением 120×120 мм — устойчивее к скручиванию на дорогах с боковым уклоном, чем круглая. Барабанные тормоза, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска AVG с подъёмом/опусканием. Электронная тормозная система TEBS 2S/2M с функцией противоопрокидывания (RSS), манометр давления в пневмоподвеске.
+6 пар коников с неоткрепляемыми стойками, грузоподъёмность 7 тонн каждая, положение регулируется вдоль рамы. Внутренняя высота коника 2 340 мм. 6 ремней для крепления сортимента. Неразборная передняя стенка перфорированного типа с крюками для каната и креплением для лома и лопаты.
+Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая противоподкатная защита. Металлический инструментальный ящик с замком. Шины TYREX 385/65R22,5.
+Максимальная полная масса 44 000 кг, грузоподъёмность 36 500 кг, длина 13 620 мм.
+При покупке в лизинг — скидка от Минпромторга 10%.
+Заводская гарантия — 12 месяцев. Поставка — 15 рабочих дней с момента предоплаты.</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
@@ -1816,14 +1817,14 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>2960000</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/09.jpg</t>
         </is>
       </c>
       <c r="S8" s="1" t="inlineStr"/>
@@ -1849,7 +1850,7 @@
       <c r="AA8" s="1" t="inlineStr"/>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>2960000</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
@@ -1857,7 +1858,11 @@
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="AD8" s="1" t="inlineStr"/>
+      <c r="AD8" s="1" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
       <c r="AE8" s="1" t="inlineStr"/>
       <c r="AF8" s="1" t="inlineStr"/>
       <c r="AG8" s="1" t="inlineStr"/>
@@ -1902,7 +1907,7 @@
       <c r="AV8" s="1" t="inlineStr"/>
       <c r="AW8" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX8" s="1" t="inlineStr">
@@ -1922,7 +1927,7 @@
       </c>
       <c r="BA8" s="1" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="BB8" s="1" t="inlineStr">
@@ -1944,7 +1949,7 @@
       <c r="C9" s="1" t="inlineStr"/>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>tonar-k4u-p0002033</t>
+          <t>steelbear-pl24l-ea653666</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -1961,11 +1966,12 @@
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
-VIN X0T998910P0002033.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
+Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
+Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
+Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
+Поставка под заказ, срок — уточняйте.</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
@@ -1975,14 +1981,14 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr"/>
@@ -2008,12 +2014,12 @@
       <c r="AA9" s="1" t="inlineStr"/>
       <c r="AB9" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr"/>
@@ -2027,7 +2033,7 @@
       <c r="AL9" s="1" t="inlineStr"/>
       <c r="AM9" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN9" s="1" t="inlineStr"/>
@@ -2038,12 +2044,12 @@
       </c>
       <c r="AP9" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>Steelbear</t>
         </is>
       </c>
       <c r="AQ9" s="1" t="inlineStr">
         <is>
-          <t>K4-U (99891)</t>
+          <t>PL-24L</t>
         </is>
       </c>
       <c r="AR9" s="1" t="inlineStr">
@@ -2053,44 +2059,40 @@
       </c>
       <c r="AS9" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT9" s="1" t="inlineStr"/>
       <c r="AU9" s="1" t="inlineStr"/>
-      <c r="AV9" s="1" t="inlineStr">
-        <is>
-          <t>X0T998910P0002033</t>
-        </is>
-      </c>
+      <c r="AV9" s="1" t="inlineStr"/>
       <c r="AW9" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX9" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY9" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ9" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA9" s="1" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="BB9" s="1" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="BC9" s="1" t="inlineStr"/>
@@ -2107,7 +2109,7 @@
       <c r="C10" s="1" t="inlineStr"/>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>v-trailer-329d-r0000119</t>
+          <t>tonar-k4u-p0002033</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -2124,10 +2126,10 @@
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-VIN XZFVKRP3DR0000119.
+          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
+4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
+Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
+VIN X0T998910P0002033.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
@@ -2138,14 +2140,14 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr"/>
@@ -2171,7 +2173,7 @@
       <c r="AA10" s="1" t="inlineStr"/>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
@@ -2201,12 +2203,12 @@
       </c>
       <c r="AP10" s="1" t="inlineStr">
         <is>
-          <t>V-Trailer</t>
+          <t>Тонар</t>
         </is>
       </c>
       <c r="AQ10" s="1" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>K4-U (99891)</t>
         </is>
       </c>
       <c r="AR10" s="1" t="inlineStr">
@@ -2216,14 +2218,14 @@
       </c>
       <c r="AS10" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT10" s="1" t="inlineStr"/>
       <c r="AU10" s="1" t="inlineStr"/>
       <c r="AV10" s="1" t="inlineStr">
         <is>
-          <t>XZFVKRP3DR0000119</t>
+          <t>X0T998910P0002033</t>
         </is>
       </c>
       <c r="AW10" s="1" t="inlineStr">
@@ -2233,12 +2235,12 @@
       </c>
       <c r="AX10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY10" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ10" s="1" t="inlineStr">
@@ -2248,21 +2250,184 @@
       </c>
       <c r="BA10" s="1" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="BB10" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC10" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="BC10" s="1" t="inlineStr"/>
       <c r="BD10" s="1" t="inlineStr"/>
       <c r="BE10" s="1" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr"/>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>v-trailer-329d-r0000119</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr"/>
+      <c r="F11" s="1" t="inlineStr"/>
+      <c r="G11" s="1" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+VIN XZFVKRP3DR0000119.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="P11" s="1" t="inlineStr"/>
+      <c r="Q11" s="1" t="inlineStr"/>
+      <c r="R11" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+        </is>
+      </c>
+      <c r="S11" s="1" t="inlineStr"/>
+      <c r="T11" s="1" t="inlineStr"/>
+      <c r="U11" s="1" t="inlineStr"/>
+      <c r="V11" s="1" t="inlineStr"/>
+      <c r="W11" s="1" t="inlineStr"/>
+      <c r="X11" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y11" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z11" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA11" s="1" t="inlineStr"/>
+      <c r="AB11" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="AC11" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD11" s="1" t="inlineStr"/>
+      <c r="AE11" s="1" t="inlineStr"/>
+      <c r="AF11" s="1" t="inlineStr"/>
+      <c r="AG11" s="1" t="inlineStr"/>
+      <c r="AH11" s="1" t="inlineStr"/>
+      <c r="AI11" s="1" t="inlineStr"/>
+      <c r="AJ11" s="1" t="inlineStr"/>
+      <c r="AK11" s="1" t="inlineStr"/>
+      <c r="AL11" s="1" t="inlineStr"/>
+      <c r="AM11" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN11" s="1" t="inlineStr"/>
+      <c r="AO11" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP11" s="1" t="inlineStr">
+        <is>
+          <t>V-Trailer</t>
+        </is>
+      </c>
+      <c r="AQ11" s="1" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AR11" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS11" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT11" s="1" t="inlineStr"/>
+      <c r="AU11" s="1" t="inlineStr"/>
+      <c r="AV11" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
+      <c r="AW11" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX11" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY11" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ11" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA11" s="1" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB11" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC11" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="BD11" s="1" t="inlineStr"/>
+      <c r="BE11" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -1149,7 +1149,7 @@
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/10.jpg</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -437,7 +437,7 @@
     <col width="40" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
     <col width="17" customWidth="1" min="22" max="22"/>
     <col width="31" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
@@ -817,7 +817,11 @@
       </c>
       <c r="S2" s="1" t="inlineStr"/>
       <c r="T2" s="1" t="inlineStr"/>
-      <c r="U2" s="1" t="inlineStr"/>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V2" s="1" t="inlineStr"/>
       <c r="W2" s="1" t="inlineStr"/>
       <c r="X2" s="1" t="inlineStr">
@@ -983,7 +987,11 @@
       </c>
       <c r="S3" s="1" t="inlineStr"/>
       <c r="T3" s="1" t="inlineStr"/>
-      <c r="U3" s="1" t="inlineStr"/>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V3" s="1" t="inlineStr"/>
       <c r="W3" s="1" t="inlineStr"/>
       <c r="X3" s="1" t="inlineStr">
@@ -1154,7 +1162,11 @@
       </c>
       <c r="S4" s="1" t="inlineStr"/>
       <c r="T4" s="1" t="inlineStr"/>
-      <c r="U4" s="1" t="inlineStr"/>
+      <c r="U4" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V4" s="1" t="inlineStr"/>
       <c r="W4" s="1" t="inlineStr"/>
       <c r="X4" s="1" t="inlineStr">
@@ -1325,7 +1337,11 @@
       </c>
       <c r="S5" s="1" t="inlineStr"/>
       <c r="T5" s="1" t="inlineStr"/>
-      <c r="U5" s="1" t="inlineStr"/>
+      <c r="U5" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V5" s="1" t="inlineStr"/>
       <c r="W5" s="1" t="inlineStr"/>
       <c r="X5" s="1" t="inlineStr">
@@ -1496,7 +1512,11 @@
       </c>
       <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
-      <c r="U6" s="1" t="inlineStr"/>
+      <c r="U6" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V6" s="1" t="inlineStr"/>
       <c r="W6" s="1" t="inlineStr"/>
       <c r="X6" s="1" t="inlineStr">
@@ -1664,7 +1684,11 @@
       </c>
       <c r="S7" s="1" t="inlineStr"/>
       <c r="T7" s="1" t="inlineStr"/>
-      <c r="U7" s="1" t="inlineStr"/>
+      <c r="U7" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V7" s="1" t="inlineStr"/>
       <c r="W7" s="1" t="inlineStr"/>
       <c r="X7" s="1" t="inlineStr">
@@ -1695,7 +1719,7 @@
       </c>
       <c r="AD7" s="1" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" s="1" t="inlineStr"/>
@@ -1829,7 +1853,11 @@
       </c>
       <c r="S8" s="1" t="inlineStr"/>
       <c r="T8" s="1" t="inlineStr"/>
-      <c r="U8" s="1" t="inlineStr"/>
+      <c r="U8" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V8" s="1" t="inlineStr"/>
       <c r="W8" s="1" t="inlineStr"/>
       <c r="X8" s="1" t="inlineStr">
@@ -1860,7 +1888,7 @@
       </c>
       <c r="AD8" s="1" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" s="1" t="inlineStr"/>
@@ -1993,7 +2021,11 @@
       </c>
       <c r="S9" s="1" t="inlineStr"/>
       <c r="T9" s="1" t="inlineStr"/>
-      <c r="U9" s="1" t="inlineStr"/>
+      <c r="U9" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V9" s="1" t="inlineStr"/>
       <c r="W9" s="1" t="inlineStr"/>
       <c r="X9" s="1" t="inlineStr">
@@ -2152,7 +2184,11 @@
       </c>
       <c r="S10" s="1" t="inlineStr"/>
       <c r="T10" s="1" t="inlineStr"/>
-      <c r="U10" s="1" t="inlineStr"/>
+      <c r="U10" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V10" s="1" t="inlineStr"/>
       <c r="W10" s="1" t="inlineStr"/>
       <c r="X10" s="1" t="inlineStr">
@@ -2315,7 +2351,11 @@
       </c>
       <c r="S11" s="1" t="inlineStr"/>
       <c r="T11" s="1" t="inlineStr"/>
-      <c r="U11" s="1" t="inlineStr"/>
+      <c r="U11" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
       <c r="V11" s="1" t="inlineStr"/>
       <c r="W11" s="1" t="inlineStr"/>
       <c r="X11" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AD7" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="AE7" s="1" t="inlineStr"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="AD8" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>296000</t>
         </is>
       </c>
       <c r="AE8" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -1157,7 +1157,7 @@
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-10.jpg</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/04.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-04.jpg</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-06.jpg</t>
         </is>
       </c>
       <c r="S6" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2346,7 +2346,7 @@
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
         </is>
       </c>
       <c r="S11" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -982,7 +982,7 @@
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/09.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-09.jpg</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -1994,12 +1994,14 @@
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L BPW Heavy Duty), 2024 год выпуска, под заказ.
-Усиленное шасси из двутавровых лонжеронов, 3 оси BPW Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L SAF Heavy Duty), 2024 год выпуска, б/у, в наличии.
+Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
 6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
 Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Заводская гарантия — 24 месяца, от сквозной коррозии — 10 лет.
-Поставка под заказ, срок — уточняйте.</t>
+Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
+Документы в порядке.
+VIN XWZ9412LLR1202021.
+Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
@@ -2051,7 +2053,7 @@
       </c>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr"/>
@@ -2065,7 +2067,7 @@
       <c r="AL9" s="1" t="inlineStr"/>
       <c r="AM9" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN9" s="1" t="inlineStr"/>
@@ -2096,7 +2098,11 @@
       </c>
       <c r="AT9" s="1" t="inlineStr"/>
       <c r="AU9" s="1" t="inlineStr"/>
-      <c r="AV9" s="1" t="inlineStr"/>
+      <c r="AV9" s="1" t="inlineStr">
+        <is>
+          <t>XWZ9412LLR1202021</t>
+        </is>
+      </c>
       <c r="AW9" s="1" t="inlineStr">
         <is>
           <t>2024</t>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -794,7 +794,6 @@
 4 оси (3 + выносная балансирная), тормоза дисковые, ABS SORL. Подвеска пневматическая, с функцией подъёма осей — меньше износ резины на порожняке и разворотах. Шины 385/55R22.5, комплект 8+1 запасное.
 Берёт контейнеры 20', 30', 40' и High Cube — под большинство стандартных грузоперевозок без переоборудования. Разрешённая максимальная масса 47 000 кг, грузоподъёмность 41 000 кг. Высота погрузки 1 100 мм.
 Инструментальный ящик Daken, полный комплект пневморазводки и ЭБС.
-VIN EAR853375R0000773.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
@@ -2000,7 +1999,6 @@
 Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
 Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
 Документы в порядке.
-VIN XWZ9412LLR1202021.
 Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
@@ -2167,7 +2165,6 @@
           <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
 4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
 Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
-VIN X0T998910P0002033.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
@@ -2334,7 +2331,6 @@
           <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
 Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
 13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-VIN XZFVKRP3DR0000119.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>1390000</t>
+          <t>1890000</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -841,7 +841,7 @@
       <c r="AA2" s="1" t="inlineStr"/>
       <c r="AB2" s="1" t="inlineStr">
         <is>
-          <t>1390000</t>
+          <t>1890000</t>
         </is>
       </c>
       <c r="AC2" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE11"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -459,7 +459,7 @@
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="17" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="25" customWidth="1" min="45" max="45"/>
     <col width="11" customWidth="1" min="46" max="46"/>
@@ -2145,7 +2145,7 @@
       <c r="C10" s="1" t="inlineStr"/>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>tonar-k4u-p0002033</t>
+          <t>tonar-b313-9888</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -2162,10 +2162,12 @@
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины на порожняке. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 150 000 ₽.
+Скидка от производителя на линейку бортовых прицепов (10%): −315 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −315 000 ₽.
+Итоговая цена при лизинге: 2 520 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
@@ -2175,14 +2177,14 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>3150000</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/10.jpg</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr"/>
@@ -2212,17 +2214,25 @@
       <c r="AA10" s="1" t="inlineStr"/>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>3150000</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD10" s="1" t="inlineStr"/>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD10" s="1" t="inlineStr">
+        <is>
+          <t>315000</t>
+        </is>
+      </c>
       <c r="AE10" s="1" t="inlineStr"/>
-      <c r="AF10" s="1" t="inlineStr"/>
+      <c r="AF10" s="1" t="inlineStr">
+        <is>
+          <t>315000</t>
+        </is>
+      </c>
       <c r="AG10" s="1" t="inlineStr"/>
       <c r="AH10" s="1" t="inlineStr"/>
       <c r="AI10" s="1" t="inlineStr"/>
@@ -2231,7 +2241,7 @@
       <c r="AL10" s="1" t="inlineStr"/>
       <c r="AM10" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN10" s="1" t="inlineStr"/>
@@ -2247,7 +2257,7 @@
       </c>
       <c r="AQ10" s="1" t="inlineStr">
         <is>
-          <t>K4-U (99891)</t>
+          <t>B3-13 (9888)</t>
         </is>
       </c>
       <c r="AR10" s="1" t="inlineStr">
@@ -2257,24 +2267,20 @@
       </c>
       <c r="AS10" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Бортовой</t>
         </is>
       </c>
       <c r="AT10" s="1" t="inlineStr"/>
       <c r="AU10" s="1" t="inlineStr"/>
-      <c r="AV10" s="1" t="inlineStr">
-        <is>
-          <t>X0T998910P0002033</t>
-        </is>
-      </c>
+      <c r="AV10" s="1" t="inlineStr"/>
       <c r="AW10" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY10" s="1" t="inlineStr">
@@ -2287,14 +2293,10 @@
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA10" s="1" t="inlineStr">
-        <is>
-          <t>37800</t>
-        </is>
-      </c>
+      <c r="BA10" s="1" t="inlineStr"/>
       <c r="BB10" s="1" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="BC10" s="1" t="inlineStr"/>
@@ -2311,7 +2313,7 @@
       <c r="C11" s="1" t="inlineStr"/>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>v-trailer-329d-r0000119</t>
+          <t>tonar-k4u-99891-order</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -2328,10 +2330,13 @@
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 4 оси, вынесенная вперёд передняя ось на 2560 мм — меньше нагрузка на дорогу. ССУ=1100 мм, шины 385/55-R22.5. Берёт контейнеры 1×20', 2×20', 1×30', 1×40' High Cube. Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
+Скидка от производителя на линейку контейнеровозов (5%): −160 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
+Итоговая цена при лизинге: 2 720 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.
+(У нас также есть эта же модель б/у, в наличии, дешевле — уточняйте по телефону, если новый под заказ не подходит по срокам.)</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -2341,14 +2346,14 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/10.jpg</t>
         </is>
       </c>
       <c r="S11" s="1" t="inlineStr"/>
@@ -2378,17 +2383,25 @@
       <c r="AA11" s="1" t="inlineStr"/>
       <c r="AB11" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD11" s="1" t="inlineStr"/>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD11" s="1" t="inlineStr">
+        <is>
+          <t>320000</t>
+        </is>
+      </c>
       <c r="AE11" s="1" t="inlineStr"/>
-      <c r="AF11" s="1" t="inlineStr"/>
+      <c r="AF11" s="1" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
       <c r="AG11" s="1" t="inlineStr"/>
       <c r="AH11" s="1" t="inlineStr"/>
       <c r="AI11" s="1" t="inlineStr"/>
@@ -2397,7 +2410,7 @@
       <c r="AL11" s="1" t="inlineStr"/>
       <c r="AM11" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN11" s="1" t="inlineStr"/>
@@ -2408,12 +2421,12 @@
       </c>
       <c r="AP11" s="1" t="inlineStr">
         <is>
-          <t>V-Trailer</t>
+          <t>Тонар</t>
         </is>
       </c>
       <c r="AQ11" s="1" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>K4-U (99891)</t>
         </is>
       </c>
       <c r="AR11" s="1" t="inlineStr">
@@ -2423,29 +2436,25 @@
       </c>
       <c r="AS11" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT11" s="1" t="inlineStr"/>
       <c r="AU11" s="1" t="inlineStr"/>
-      <c r="AV11" s="1" t="inlineStr">
-        <is>
-          <t>XZFVKRP3DR0000119</t>
-        </is>
-      </c>
+      <c r="AV11" s="1" t="inlineStr"/>
       <c r="AW11" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX11" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY11" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ11" s="1" t="inlineStr">
@@ -2453,23 +2462,1337 @@
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA11" s="1" t="inlineStr">
-        <is>
-          <t>32300</t>
-        </is>
-      </c>
+      <c r="BA11" s="1" t="inlineStr"/>
       <c r="BB11" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC11" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="BC11" s="1" t="inlineStr"/>
       <c r="BD11" s="1" t="inlineStr"/>
       <c r="BE11" s="1" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr"/>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>tonar-k4u-p0002033</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr"/>
+      <c r="F12" s="1" t="inlineStr"/>
+      <c r="G12" s="1" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
+4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
+Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t>1690000</t>
+        </is>
+      </c>
+      <c r="P12" s="1" t="inlineStr"/>
+      <c r="Q12" s="1" t="inlineStr"/>
+      <c r="R12" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
+        </is>
+      </c>
+      <c r="S12" s="1" t="inlineStr"/>
+      <c r="T12" s="1" t="inlineStr"/>
+      <c r="U12" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V12" s="1" t="inlineStr"/>
+      <c r="W12" s="1" t="inlineStr"/>
+      <c r="X12" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y12" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z12" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA12" s="1" t="inlineStr"/>
+      <c r="AB12" s="1" t="inlineStr">
+        <is>
+          <t>1690000</t>
+        </is>
+      </c>
+      <c r="AC12" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD12" s="1" t="inlineStr"/>
+      <c r="AE12" s="1" t="inlineStr"/>
+      <c r="AF12" s="1" t="inlineStr"/>
+      <c r="AG12" s="1" t="inlineStr"/>
+      <c r="AH12" s="1" t="inlineStr"/>
+      <c r="AI12" s="1" t="inlineStr"/>
+      <c r="AJ12" s="1" t="inlineStr"/>
+      <c r="AK12" s="1" t="inlineStr"/>
+      <c r="AL12" s="1" t="inlineStr"/>
+      <c r="AM12" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN12" s="1" t="inlineStr"/>
+      <c r="AO12" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP12" s="1" t="inlineStr">
+        <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="AQ12" s="1" t="inlineStr">
+        <is>
+          <t>K4-U (99891)</t>
+        </is>
+      </c>
+      <c r="AR12" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS12" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
+      <c r="AT12" s="1" t="inlineStr"/>
+      <c r="AU12" s="1" t="inlineStr"/>
+      <c r="AV12" s="1" t="inlineStr">
+        <is>
+          <t>X0T998910P0002033</t>
+        </is>
+      </c>
+      <c r="AW12" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX12" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AY12" s="1" t="inlineStr">
+        <is>
+          <t>Рессорная</t>
+        </is>
+      </c>
+      <c r="AZ12" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA12" s="1" t="inlineStr">
+        <is>
+          <t>37800</t>
+        </is>
+      </c>
+      <c r="BB12" s="1" t="inlineStr">
+        <is>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="BC12" s="1" t="inlineStr"/>
+      <c r="BD12" s="1" t="inlineStr"/>
+      <c r="BE12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr"/>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>tonar-l3-9445</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+      <c r="G13" s="1" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ на порожняке. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
+Скидка от производителя на линейку лесовозов (5%): −160 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
+Итоговая цена при лизинге: 2 720 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>3200000</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr"/>
+      <c r="Q13" s="1" t="inlineStr"/>
+      <c r="R13" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/10.jpg</t>
+        </is>
+      </c>
+      <c r="S13" s="1" t="inlineStr"/>
+      <c r="T13" s="1" t="inlineStr"/>
+      <c r="U13" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V13" s="1" t="inlineStr"/>
+      <c r="W13" s="1" t="inlineStr"/>
+      <c r="X13" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y13" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z13" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA13" s="1" t="inlineStr"/>
+      <c r="AB13" s="1" t="inlineStr">
+        <is>
+          <t>3200000</t>
+        </is>
+      </c>
+      <c r="AC13" s="1" t="inlineStr">
+        <is>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD13" s="1" t="inlineStr">
+        <is>
+          <t>320000</t>
+        </is>
+      </c>
+      <c r="AE13" s="1" t="inlineStr"/>
+      <c r="AF13" s="1" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="AG13" s="1" t="inlineStr"/>
+      <c r="AH13" s="1" t="inlineStr"/>
+      <c r="AI13" s="1" t="inlineStr"/>
+      <c r="AJ13" s="1" t="inlineStr"/>
+      <c r="AK13" s="1" t="inlineStr"/>
+      <c r="AL13" s="1" t="inlineStr"/>
+      <c r="AM13" s="1" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AN13" s="1" t="inlineStr"/>
+      <c r="AO13" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP13" s="1" t="inlineStr">
+        <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="AQ13" s="1" t="inlineStr">
+        <is>
+          <t>L3 (9445)</t>
+        </is>
+      </c>
+      <c r="AR13" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS13" s="1" t="inlineStr">
+        <is>
+          <t>Лесовоз (сортиментовоз)</t>
+        </is>
+      </c>
+      <c r="AT13" s="1" t="inlineStr"/>
+      <c r="AU13" s="1" t="inlineStr"/>
+      <c r="AV13" s="1" t="inlineStr"/>
+      <c r="AW13" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AX13" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY13" s="1" t="inlineStr">
+        <is>
+          <t>Рессорная</t>
+        </is>
+      </c>
+      <c r="AZ13" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
+      <c r="BA13" s="1" t="inlineStr"/>
+      <c r="BB13" s="1" t="inlineStr"/>
+      <c r="BC13" s="1" t="inlineStr"/>
+      <c r="BD13" s="1" t="inlineStr"/>
+      <c r="BE13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr"/>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>tonar-reef-r313</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+      <c r="G14" s="1" t="inlineStr"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 85 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
+В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины (у нас в парке такой есть от 4 850 000 ₽ по прайсу завода без холодильной установки).
+Цена: 7 000 000 ₽ (на эту линейку скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 6 500 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>7000000</t>
+        </is>
+      </c>
+      <c r="P14" s="1" t="inlineStr"/>
+      <c r="Q14" s="1" t="inlineStr"/>
+      <c r="R14" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg</t>
+        </is>
+      </c>
+      <c r="S14" s="1" t="inlineStr"/>
+      <c r="T14" s="1" t="inlineStr"/>
+      <c r="U14" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V14" s="1" t="inlineStr"/>
+      <c r="W14" s="1" t="inlineStr"/>
+      <c r="X14" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y14" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z14" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA14" s="1" t="inlineStr"/>
+      <c r="AB14" s="1" t="inlineStr">
+        <is>
+          <t>7000000</t>
+        </is>
+      </c>
+      <c r="AC14" s="1" t="inlineStr">
+        <is>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD14" s="1" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="AE14" s="1" t="inlineStr"/>
+      <c r="AF14" s="1" t="inlineStr"/>
+      <c r="AG14" s="1" t="inlineStr"/>
+      <c r="AH14" s="1" t="inlineStr"/>
+      <c r="AI14" s="1" t="inlineStr"/>
+      <c r="AJ14" s="1" t="inlineStr"/>
+      <c r="AK14" s="1" t="inlineStr"/>
+      <c r="AL14" s="1" t="inlineStr"/>
+      <c r="AM14" s="1" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AN14" s="1" t="inlineStr"/>
+      <c r="AO14" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP14" s="1" t="inlineStr">
+        <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="AQ14" s="1" t="inlineStr">
+        <is>
+          <t>R3-13</t>
+        </is>
+      </c>
+      <c r="AR14" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS14" s="1" t="inlineStr">
+        <is>
+          <t>Рефрижератор</t>
+        </is>
+      </c>
+      <c r="AT14" s="1" t="inlineStr"/>
+      <c r="AU14" s="1" t="inlineStr"/>
+      <c r="AV14" s="1" t="inlineStr"/>
+      <c r="AW14" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AX14" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY14" s="1" t="inlineStr">
+        <is>
+          <t>Рессорная</t>
+        </is>
+      </c>
+      <c r="AZ14" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA14" s="1" t="inlineStr"/>
+      <c r="BB14" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC14" s="1" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="BD14" s="1" t="inlineStr"/>
+      <c r="BE14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr"/>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>tonar-samosval-9595</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+      <c r="G15" s="1" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr"/>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп самосвальный Тонар 9595, четырёхосный, тент с боковым намотом, рычажная подвеска, дисковые тормоза. Новое, под заказ у завода-изготовителя.
+Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
+Итоговая цена при лизинге: 3 780 000 ₽.
+Заводская гарантия — 12 месяцев. Точную комплектацию (объём кузова, борта) уточняйте при заказе.</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t>4200000</t>
+        </is>
+      </c>
+      <c r="P15" s="1" t="inlineStr"/>
+      <c r="Q15" s="1" t="inlineStr"/>
+      <c r="R15" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/03.jpg</t>
+        </is>
+      </c>
+      <c r="S15" s="1" t="inlineStr"/>
+      <c r="T15" s="1" t="inlineStr"/>
+      <c r="U15" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V15" s="1" t="inlineStr"/>
+      <c r="W15" s="1" t="inlineStr"/>
+      <c r="X15" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y15" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z15" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA15" s="1" t="inlineStr"/>
+      <c r="AB15" s="1" t="inlineStr">
+        <is>
+          <t>4200000</t>
+        </is>
+      </c>
+      <c r="AC15" s="1" t="inlineStr">
+        <is>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD15" s="1" t="inlineStr">
+        <is>
+          <t>420000</t>
+        </is>
+      </c>
+      <c r="AE15" s="1" t="inlineStr"/>
+      <c r="AF15" s="1" t="inlineStr"/>
+      <c r="AG15" s="1" t="inlineStr"/>
+      <c r="AH15" s="1" t="inlineStr"/>
+      <c r="AI15" s="1" t="inlineStr"/>
+      <c r="AJ15" s="1" t="inlineStr"/>
+      <c r="AK15" s="1" t="inlineStr"/>
+      <c r="AL15" s="1" t="inlineStr"/>
+      <c r="AM15" s="1" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AN15" s="1" t="inlineStr"/>
+      <c r="AO15" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP15" s="1" t="inlineStr">
+        <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="AQ15" s="1" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="AR15" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS15" s="1" t="inlineStr">
+        <is>
+          <t>Самосвальный</t>
+        </is>
+      </c>
+      <c r="AT15" s="1" t="inlineStr"/>
+      <c r="AU15" s="1" t="inlineStr"/>
+      <c r="AV15" s="1" t="inlineStr"/>
+      <c r="AW15" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AX15" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AY15" s="1" t="inlineStr">
+        <is>
+          <t>Рессорная</t>
+        </is>
+      </c>
+      <c r="AZ15" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA15" s="1" t="inlineStr"/>
+      <c r="BB15" s="1" t="inlineStr"/>
+      <c r="BC15" s="1" t="inlineStr"/>
+      <c r="BD15" s="1" t="inlineStr"/>
+      <c r="BE15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>tonar-sdp489-95895</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+      <c r="G16" s="1" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr"/>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп со сдвижными полами Тонар SDP4-89 (95895), 4 оси (первая вынесенная), габаритная длина 14,6 м, погрузочная длина 14,1 м, алюминиевый кузов, объём 89 м³, ССУ=1150 мм. Новое, под заказ у завода-изготовителя.
+Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без опрокидывания кузова — можно разгружаться на неровных площадках и под низкими навесами, где самосвал не встанет. Универсален под насыпные грузы: щепа, зерно, песок и т.п.
+Цена: 7 650 000 ₽ (на эту линейку скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 7 150 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>7650000</t>
+        </is>
+      </c>
+      <c r="P16" s="1" t="inlineStr"/>
+      <c r="Q16" s="1" t="inlineStr"/>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/03.jpg</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="inlineStr"/>
+      <c r="T16" s="1" t="inlineStr"/>
+      <c r="U16" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V16" s="1" t="inlineStr"/>
+      <c r="W16" s="1" t="inlineStr"/>
+      <c r="X16" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y16" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z16" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA16" s="1" t="inlineStr"/>
+      <c r="AB16" s="1" t="inlineStr">
+        <is>
+          <t>7650000</t>
+        </is>
+      </c>
+      <c r="AC16" s="1" t="inlineStr">
+        <is>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD16" s="1" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="AE16" s="1" t="inlineStr"/>
+      <c r="AF16" s="1" t="inlineStr"/>
+      <c r="AG16" s="1" t="inlineStr"/>
+      <c r="AH16" s="1" t="inlineStr"/>
+      <c r="AI16" s="1" t="inlineStr"/>
+      <c r="AJ16" s="1" t="inlineStr"/>
+      <c r="AK16" s="1" t="inlineStr"/>
+      <c r="AL16" s="1" t="inlineStr"/>
+      <c r="AM16" s="1" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AN16" s="1" t="inlineStr"/>
+      <c r="AO16" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP16" s="1" t="inlineStr">
+        <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="AQ16" s="1" t="inlineStr">
+        <is>
+          <t>SDP4-89 (95895)</t>
+        </is>
+      </c>
+      <c r="AR16" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS16" s="1" t="inlineStr">
+        <is>
+          <t>Щеповоз</t>
+        </is>
+      </c>
+      <c r="AT16" s="1" t="inlineStr"/>
+      <c r="AU16" s="1" t="inlineStr"/>
+      <c r="AV16" s="1" t="inlineStr"/>
+      <c r="AW16" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AX16" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AY16" s="1" t="inlineStr">
+        <is>
+          <t>Рессорная</t>
+        </is>
+      </c>
+      <c r="AZ16" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA16" s="1" t="inlineStr"/>
+      <c r="BB16" s="1" t="inlineStr">
+        <is>
+          <t>14600</t>
+        </is>
+      </c>
+      <c r="BC16" s="1" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="BD16" s="1" t="inlineStr"/>
+      <c r="BE16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr"/>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>tonar-t313-9888</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+      <c r="G17" s="1" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr"/>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная, объём 91,4 м³. Дисковые оси, ССУ-1150 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 800 000 ₽.
+Скидка от производителя на линейку шторных прицепов (10%): −380 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −380 000 ₽.
+Итоговая цена при лизинге: 3 040 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>3800000</t>
+        </is>
+      </c>
+      <c r="P17" s="1" t="inlineStr"/>
+      <c r="Q17" s="1" t="inlineStr"/>
+      <c r="R17" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/10.jpg</t>
+        </is>
+      </c>
+      <c r="S17" s="1" t="inlineStr"/>
+      <c r="T17" s="1" t="inlineStr"/>
+      <c r="U17" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V17" s="1" t="inlineStr"/>
+      <c r="W17" s="1" t="inlineStr"/>
+      <c r="X17" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y17" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z17" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA17" s="1" t="inlineStr"/>
+      <c r="AB17" s="1" t="inlineStr">
+        <is>
+          <t>3800000</t>
+        </is>
+      </c>
+      <c r="AC17" s="1" t="inlineStr">
+        <is>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD17" s="1" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="AE17" s="1" t="inlineStr"/>
+      <c r="AF17" s="1" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="AG17" s="1" t="inlineStr"/>
+      <c r="AH17" s="1" t="inlineStr"/>
+      <c r="AI17" s="1" t="inlineStr"/>
+      <c r="AJ17" s="1" t="inlineStr"/>
+      <c r="AK17" s="1" t="inlineStr"/>
+      <c r="AL17" s="1" t="inlineStr"/>
+      <c r="AM17" s="1" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AN17" s="1" t="inlineStr"/>
+      <c r="AO17" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP17" s="1" t="inlineStr">
+        <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="AQ17" s="1" t="inlineStr">
+        <is>
+          <t>T3-13 (9888)</t>
+        </is>
+      </c>
+      <c r="AR17" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS17" s="1" t="inlineStr">
+        <is>
+          <t>Шторно-бортовой</t>
+        </is>
+      </c>
+      <c r="AT17" s="1" t="inlineStr"/>
+      <c r="AU17" s="1" t="inlineStr"/>
+      <c r="AV17" s="1" t="inlineStr"/>
+      <c r="AW17" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AX17" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY17" s="1" t="inlineStr">
+        <is>
+          <t>Рессорная</t>
+        </is>
+      </c>
+      <c r="AZ17" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA17" s="1" t="inlineStr"/>
+      <c r="BB17" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC17" s="1" t="inlineStr">
+        <is>
+          <t>91.4</t>
+        </is>
+      </c>
+      <c r="BD17" s="1" t="inlineStr"/>
+      <c r="BE17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>tonar-zernovoz-95941</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+      <c r="G18" s="1" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr"/>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп-зерновоз Тонар 95941, алюминиевый кузов с боковыми люками, объём 50 м³, ССУ=1200/1350 мм. Новое, под заказ у завода-изготовителя.
+Цена: 5 600 000 ₽ (на линейку зерновозов скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 5 100 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O18" s="1" t="inlineStr">
+        <is>
+          <t>5600000</t>
+        </is>
+      </c>
+      <c r="P18" s="1" t="inlineStr"/>
+      <c r="Q18" s="1" t="inlineStr"/>
+      <c r="R18" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/05.jpg</t>
+        </is>
+      </c>
+      <c r="S18" s="1" t="inlineStr"/>
+      <c r="T18" s="1" t="inlineStr"/>
+      <c r="U18" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V18" s="1" t="inlineStr"/>
+      <c r="W18" s="1" t="inlineStr"/>
+      <c r="X18" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y18" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z18" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA18" s="1" t="inlineStr"/>
+      <c r="AB18" s="1" t="inlineStr">
+        <is>
+          <t>5600000</t>
+        </is>
+      </c>
+      <c r="AC18" s="1" t="inlineStr">
+        <is>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD18" s="1" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="AE18" s="1" t="inlineStr"/>
+      <c r="AF18" s="1" t="inlineStr"/>
+      <c r="AG18" s="1" t="inlineStr"/>
+      <c r="AH18" s="1" t="inlineStr"/>
+      <c r="AI18" s="1" t="inlineStr"/>
+      <c r="AJ18" s="1" t="inlineStr"/>
+      <c r="AK18" s="1" t="inlineStr"/>
+      <c r="AL18" s="1" t="inlineStr"/>
+      <c r="AM18" s="1" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AN18" s="1" t="inlineStr"/>
+      <c r="AO18" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP18" s="1" t="inlineStr">
+        <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="AQ18" s="1" t="inlineStr">
+        <is>
+          <t>95941</t>
+        </is>
+      </c>
+      <c r="AR18" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS18" s="1" t="inlineStr">
+        <is>
+          <t>Зерновоз</t>
+        </is>
+      </c>
+      <c r="AT18" s="1" t="inlineStr"/>
+      <c r="AU18" s="1" t="inlineStr"/>
+      <c r="AV18" s="1" t="inlineStr"/>
+      <c r="AW18" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AX18" s="1" t="inlineStr"/>
+      <c r="AY18" s="1" t="inlineStr">
+        <is>
+          <t>Рессорная</t>
+        </is>
+      </c>
+      <c r="AZ18" s="1" t="inlineStr"/>
+      <c r="BA18" s="1" t="inlineStr"/>
+      <c r="BB18" s="1" t="inlineStr"/>
+      <c r="BC18" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="BD18" s="1" t="inlineStr"/>
+      <c r="BE18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr"/>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>v-trailer-329d-r0000119</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+      <c r="G19" s="1" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr"/>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M19" s="1" t="inlineStr">
+        <is>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O19" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="P19" s="1" t="inlineStr"/>
+      <c r="Q19" s="1" t="inlineStr"/>
+      <c r="R19" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
+        </is>
+      </c>
+      <c r="S19" s="1" t="inlineStr"/>
+      <c r="T19" s="1" t="inlineStr"/>
+      <c r="U19" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V19" s="1" t="inlineStr"/>
+      <c r="W19" s="1" t="inlineStr"/>
+      <c r="X19" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y19" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z19" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA19" s="1" t="inlineStr"/>
+      <c r="AB19" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="AC19" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD19" s="1" t="inlineStr"/>
+      <c r="AE19" s="1" t="inlineStr"/>
+      <c r="AF19" s="1" t="inlineStr"/>
+      <c r="AG19" s="1" t="inlineStr"/>
+      <c r="AH19" s="1" t="inlineStr"/>
+      <c r="AI19" s="1" t="inlineStr"/>
+      <c r="AJ19" s="1" t="inlineStr"/>
+      <c r="AK19" s="1" t="inlineStr"/>
+      <c r="AL19" s="1" t="inlineStr"/>
+      <c r="AM19" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN19" s="1" t="inlineStr"/>
+      <c r="AO19" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP19" s="1" t="inlineStr">
+        <is>
+          <t>V-Trailer</t>
+        </is>
+      </c>
+      <c r="AQ19" s="1" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AR19" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS19" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT19" s="1" t="inlineStr"/>
+      <c r="AU19" s="1" t="inlineStr"/>
+      <c r="AV19" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
+      <c r="AW19" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX19" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY19" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ19" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA19" s="1" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB19" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC19" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="BD19" s="1" t="inlineStr"/>
+      <c r="BE19" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2293,7 +2293,11 @@
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA10" s="1" t="inlineStr"/>
+      <c r="BA10" s="1" t="inlineStr">
+        <is>
+          <t>31600</t>
+        </is>
+      </c>
       <c r="BB10" s="1" t="inlineStr">
         <is>
           <t>13600</t>
@@ -2462,7 +2466,11 @@
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA11" s="1" t="inlineStr"/>
+      <c r="BA11" s="1" t="inlineStr">
+        <is>
+          <t>37800</t>
+        </is>
+      </c>
       <c r="BB11" s="1" t="inlineStr">
         <is>
           <t>12725</t>
@@ -2796,7 +2804,11 @@
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="BA13" s="1" t="inlineStr"/>
+      <c r="BA13" s="1" t="inlineStr">
+        <is>
+          <t>36700</t>
+        </is>
+      </c>
       <c r="BB13" s="1" t="inlineStr"/>
       <c r="BC13" s="1" t="inlineStr"/>
       <c r="BD13" s="1" t="inlineStr"/>
@@ -2956,7 +2968,11 @@
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA14" s="1" t="inlineStr"/>
+      <c r="BA14" s="1" t="inlineStr">
+        <is>
+          <t>31200</t>
+        </is>
+      </c>
       <c r="BB14" s="1" t="inlineStr">
         <is>
           <t>13600</t>
@@ -2997,11 +3013,11 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп самосвальный Тонар 9595, четырёхосный, тент с боковым намотом, рычажная подвеска, дисковые тормоза. Новое, под заказ у завода-изготовителя.
+          <t>Полуприцеп самосвальный Тонар 9595 (облегчённый), объём кузова 33,6 м³, четырёхосный (первая и вторая ось подъёмные), пневматическая рычажная подвеска, дисковые тормоза. Подходит и под лёгкие сельхозкультуры, и под нерудные материалы повышенной насыпной плотности. Новое, под заказ у завода-изготовителя.
 Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
 При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
 Итоговая цена при лизинге: 3 780 000 ₽.
-Заводская гарантия — 12 месяцев. Точную комплектацию (объём кузова, борта) уточняйте при заказе.</t>
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
       <c r="N15" s="1" t="inlineStr">
@@ -3115,7 +3131,7 @@
       </c>
       <c r="AY15" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ15" s="1" t="inlineStr">
@@ -3123,9 +3139,17 @@
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA15" s="1" t="inlineStr"/>
+      <c r="BA15" s="1" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
       <c r="BB15" s="1" t="inlineStr"/>
-      <c r="BC15" s="1" t="inlineStr"/>
+      <c r="BC15" s="1" t="inlineStr">
+        <is>
+          <t>33.6</t>
+        </is>
+      </c>
       <c r="BD15" s="1" t="inlineStr"/>
       <c r="BE15" s="1" t="inlineStr"/>
     </row>
@@ -3275,7 +3299,7 @@
       </c>
       <c r="AY16" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ16" s="1" t="inlineStr">
@@ -3283,7 +3307,11 @@
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA16" s="1" t="inlineStr"/>
+      <c r="BA16" s="1" t="inlineStr">
+        <is>
+          <t>27800</t>
+        </is>
+      </c>
       <c r="BB16" s="1" t="inlineStr">
         <is>
           <t>14600</t>
@@ -3291,7 +3319,7 @@
       </c>
       <c r="BC16" s="1" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD16" s="1" t="inlineStr"/>
@@ -3455,7 +3483,11 @@
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="BA17" s="1" t="inlineStr"/>
+      <c r="BA17" s="1" t="inlineStr">
+        <is>
+          <t>31000</t>
+        </is>
+      </c>
       <c r="BB17" s="1" t="inlineStr">
         <is>
           <t>13600</t>
@@ -3607,14 +3639,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AX18" s="1" t="inlineStr"/>
+      <c r="AX18" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AY18" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ18" s="1" t="inlineStr"/>
-      <c r="BA18" s="1" t="inlineStr"/>
+      <c r="BA18" s="1" t="inlineStr">
+        <is>
+          <t>33200</t>
+        </is>
+      </c>
       <c r="BB18" s="1" t="inlineStr"/>
       <c r="BC18" s="1" t="inlineStr">
         <is>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2285,12 +2285,12 @@
       </c>
       <c r="AY10" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ10" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA10" s="1" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="AZ15" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA15" s="1" t="inlineStr">
@@ -3302,11 +3302,7 @@
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ16" s="1" t="inlineStr">
-        <is>
-          <t>Дисковые</t>
-        </is>
-      </c>
+      <c r="AZ16" s="1" t="inlineStr"/>
       <c r="BA16" s="1" t="inlineStr">
         <is>
           <t>27800</t>
@@ -3528,10 +3524,10 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-зерновоз Тонар 95941, алюминиевый кузов с боковыми люками, объём 50 м³, ССУ=1200/1350 мм. Новое, под заказ у завода-изготовителя.
-Цена: 5 600 000 ₽ (на линейку зерновозов скидка от производителя не действует).
+          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый кузов прямоугольной формы, объём 50 м³, до 31 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными люками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
+Цена: 5 400 000 ₽ (на линейку зерновозов скидка от производителя не действует).
 При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 5 100 000 ₽.
+Итоговая цена при лизинге: 4 900 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3542,7 +3538,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>5600000</t>
+          <t>5400000</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -3579,7 +3575,7 @@
       <c r="AA18" s="1" t="inlineStr"/>
       <c r="AB18" s="1" t="inlineStr">
         <is>
-          <t>5600000</t>
+          <t>5400000</t>
         </is>
       </c>
       <c r="AC18" s="1" t="inlineStr">
@@ -3649,10 +3645,14 @@
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ18" s="1" t="inlineStr"/>
+      <c r="AZ18" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
       <c r="BA18" s="1" t="inlineStr">
         <is>
-          <t>33200</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="BB18" s="1" t="inlineStr"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -3013,7 +3013,7 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп самосвальный Тонар 9595 (облегчённый), объём кузова 33,6 м³, четырёхосный (первая и вторая ось подъёмные), пневматическая рычажная подвеска, дисковые тормоза. Подходит и под лёгкие сельхозкультуры, и под нерудные материалы повышенной насыпной плотности. Новое, под заказ у завода-изготовителя.
+          <t>Полуприцеп самосвальный Тонар SH4-34 (9595) с задней разгрузкой, облегчённый, объём кузова 33,6 м³, четырёхосный, пневматическая рычажная подвеска, барабанные тормоза. Кузов полукруглой формы — сыпучий груз сходит легче, без залипания, в том числе влажный. Подходит под сыпучие строительные материалы. Тент с ручной намоткой в базе. Новое, под заказ у завода-изготовителя.
 Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
 При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
 Итоговая цена при лизинге: 3 780 000 ₽.

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AY11" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ11" s="1" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="AY13" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ13" s="1" t="inlineStr">
@@ -2809,8 +2809,16 @@
           <t>36700</t>
         </is>
       </c>
-      <c r="BB13" s="1" t="inlineStr"/>
-      <c r="BC13" s="1" t="inlineStr"/>
+      <c r="BB13" s="1" t="inlineStr">
+        <is>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="BC13" s="1" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="BD13" s="1" t="inlineStr"/>
       <c r="BE13" s="1" t="inlineStr"/>
     </row>
@@ -2960,7 +2968,7 @@
       </c>
       <c r="AY14" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ14" s="1" t="inlineStr">
@@ -3471,7 +3479,7 @@
       </c>
       <c r="AY17" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ17" s="1" t="inlineStr">
@@ -3647,7 +3655,7 @@
       </c>
       <c r="AZ18" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA18" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -3310,7 +3310,11 @@
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AZ16" s="1" t="inlineStr"/>
+      <c r="AZ16" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
       <c r="BA16" s="1" t="inlineStr">
         <is>
           <t>27800</t>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -2463,7 +2463,7 @@
       </c>
       <c r="AZ11" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA11" s="1" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="BB11" s="1" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="BC11" s="1" t="inlineStr"/>
@@ -2851,9 +2851,9 @@
         <is>
           <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 85 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
 В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины (у нас в парке такой есть от 4 850 000 ₽ по прайсу завода без холодильной установки).
-Цена: 7 000 000 ₽ (на эту линейку скидка от производителя не действует).
+Цена: 7 365 000 ₽ (на эту линейку скидка от производителя не действует).
 При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 6 500 000 ₽.
+Итоговая цена при лизинге: 6 865 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>7000000</t>
+          <t>7365000</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       <c r="AA14" s="1" t="inlineStr"/>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>7000000</t>
+          <t>7365000</t>
         </is>
       </c>
       <c r="AC14" s="1" t="inlineStr">

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE19"/>
+  <dimension ref="A1:BE20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,7 @@
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="25" customWidth="1" min="45" max="45"/>
@@ -3686,7 +3686,7 @@
       <c r="C19" s="1" t="inlineStr"/>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>v-trailer-329d-r0000119</t>
+          <t>tverstroymash-993941-0al4980</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr"/>
@@ -3703,10 +3703,12 @@
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп-тяжеловоз (трал) Тверьстроймаш 993941, исполнение RL40GW (серия Rapid), 2024 год, в наличии.
+4 оси (3+1): 1-я стационарная подъёмная, 2-я и 3-я стационарные, 4-я подруливающая — подвеска пневматическая, тормоза барабанные с АБС. Шины 235/75 R17.5, Кама.
+Грузоподъёмность технически допустимая 40 000 кг, нагрузка на ССУ тягача 15 000 кг. Раздвижная грузовая платформа (гусёк) — длина при полном раздвижении 10 790 мм, ширина 2530 мм (с уширителями до 2990 мм), высота погрузки 890 мм. Настил платформы — дерево с металлическим профилем, на гуське — дерево.
+В комплекте: 2 запасных колеса с системой вертикальной установки, 4 аппарели (Тверьстроймаш, 45 т, ручные), уширители грузовой платформы, комплект из 4 выдвижных знаков «Крупногабаритный груз» со светотехникой и стробоскопами, проблесковый маячок, система мониторинга осевых нагрузок (2 датчика) и манометры контроля на 4 оси, инструментальный ящик (480 л), комплект фитингов для контейнера 1×40', вставные стойки.
+Цвет красный (RAL 3020). Документы в порядке — СТС и спецификация на руках, VIN X89993940R0AL4980.
+Цена: 8 200 000 ₽.</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
@@ -3716,14 +3718,14 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>8200000</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr"/>
       <c r="R19" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/08.jpg</t>
         </is>
       </c>
       <c r="S19" s="1" t="inlineStr"/>
@@ -3753,7 +3755,7 @@
       <c r="AA19" s="1" t="inlineStr"/>
       <c r="AB19" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>8200000</t>
         </is>
       </c>
       <c r="AC19" s="1" t="inlineStr">
@@ -3783,12 +3785,12 @@
       </c>
       <c r="AP19" s="1" t="inlineStr">
         <is>
-          <t>V-Trailer</t>
+          <t>Тверьстроймаш</t>
         </is>
       </c>
       <c r="AQ19" s="1" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>993941</t>
         </is>
       </c>
       <c r="AR19" s="1" t="inlineStr">
@@ -3798,24 +3800,24 @@
       </c>
       <c r="AS19" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Трал (тяжеловоз)</t>
         </is>
       </c>
       <c r="AT19" s="1" t="inlineStr"/>
       <c r="AU19" s="1" t="inlineStr"/>
       <c r="AV19" s="1" t="inlineStr">
         <is>
-          <t>XZFVKRP3DR0000119</t>
+          <t>X89993940R0AL4980</t>
         </is>
       </c>
       <c r="AW19" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX19" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY19" s="1" t="inlineStr">
@@ -3825,26 +3827,192 @@
       </c>
       <c r="AZ19" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA19" s="1" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="BB19" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC19" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
+          <t>10790</t>
+        </is>
+      </c>
+      <c r="BC19" s="1" t="inlineStr"/>
       <c r="BD19" s="1" t="inlineStr"/>
       <c r="BE19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr"/>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>v-trailer-329d-r0000119</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="P20" s="1" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr"/>
+      <c r="R20" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
+        </is>
+      </c>
+      <c r="S20" s="1" t="inlineStr"/>
+      <c r="T20" s="1" t="inlineStr"/>
+      <c r="U20" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V20" s="1" t="inlineStr"/>
+      <c r="W20" s="1" t="inlineStr"/>
+      <c r="X20" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y20" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z20" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA20" s="1" t="inlineStr"/>
+      <c r="AB20" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="AC20" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD20" s="1" t="inlineStr"/>
+      <c r="AE20" s="1" t="inlineStr"/>
+      <c r="AF20" s="1" t="inlineStr"/>
+      <c r="AG20" s="1" t="inlineStr"/>
+      <c r="AH20" s="1" t="inlineStr"/>
+      <c r="AI20" s="1" t="inlineStr"/>
+      <c r="AJ20" s="1" t="inlineStr"/>
+      <c r="AK20" s="1" t="inlineStr"/>
+      <c r="AL20" s="1" t="inlineStr"/>
+      <c r="AM20" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN20" s="1" t="inlineStr"/>
+      <c r="AO20" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP20" s="1" t="inlineStr">
+        <is>
+          <t>V-Trailer</t>
+        </is>
+      </c>
+      <c r="AQ20" s="1" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AR20" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS20" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT20" s="1" t="inlineStr"/>
+      <c r="AU20" s="1" t="inlineStr"/>
+      <c r="AV20" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
+      <c r="AW20" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX20" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY20" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ20" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA20" s="1" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB20" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC20" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="BD20" s="1" t="inlineStr"/>
+      <c r="BE20" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -3707,7 +3707,7 @@
 4 оси (3+1): 1-я стационарная подъёмная, 2-я и 3-я стационарные, 4-я подруливающая — подвеска пневматическая, тормоза барабанные с АБС. Шины 235/75 R17.5, Кама.
 Грузоподъёмность технически допустимая 40 000 кг, нагрузка на ССУ тягача 15 000 кг. Раздвижная грузовая платформа (гусёк) — длина при полном раздвижении 10 790 мм, ширина 2530 мм (с уширителями до 2990 мм), высота погрузки 890 мм. Настил платформы — дерево с металлическим профилем, на гуське — дерево.
 В комплекте: 2 запасных колеса с системой вертикальной установки, 4 аппарели (Тверьстроймаш, 45 т, ручные), уширители грузовой платформы, комплект из 4 выдвижных знаков «Крупногабаритный груз» со светотехникой и стробоскопами, проблесковый маячок, система мониторинга осевых нагрузок (2 датчика) и манометры контроля на 4 оси, инструментальный ящик (480 л), комплект фитингов для контейнера 1×40', вставные стойки.
-Цвет красный (RAL 3020). Документы в порядке — СТС и спецификация на руках, VIN X89993940R0AL4980.
+Цвет красный (RAL 3020). Документы в порядке — СТС и спецификация на руках.
 Цена: 8 200 000 ₽.</t>
         </is>
       </c>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE20"/>
+  <dimension ref="A1:BE21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -773,7 +773,7 @@
       <c r="C2" s="1" t="inlineStr"/>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>interpricep-853375-r0000773</t>
+          <t>interpricep-853372-halfpipe</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -790,11 +790,12 @@
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз ИнтерПрицеп 853375, 2024 год, в работе, полностью исправен.
-4 оси (3 + выносная балансирная), тормоза дисковые, ABS SORL. Подвеска пневматическая, с функцией подъёма осей — меньше износ резины на порожняке и разворотах. Шины 385/55R22.5, комплект 8+1 запасное.
-Берёт контейнеры 20', 30', 40' и High Cube — под большинство стандартных грузоперевозок без переоборудования. Разрешённая максимальная масса 47 000 кг, грузоподъёмность 41 000 кг. Высота погрузки 1 100 мм.
-Инструментальный ящик Daken, полный комплект пневморазводки и ЭБС.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп-самосвал с задним свалом ИнтерПрицеп 853372 «Халф Пайп», 4-осный, в наличии.
+Пневмоподвеска с механизмом подъёма на первой-второй осях. Оси барабанные, 12 тонн, L1 (Китай), гидроцилиндр Atlant (Россия). Тормозная система ABS SORL (аналог WABCO). Шины 385/65R22,5 Tyrex, комплект 8+1 запасное.
+Кузов графитово-серый/чёрный, лакокрасочное покрытие двухслойное, рама — антигравийное покрытие. Толщина стенок кузова 5 мм, пола 6 мм. Задний борт с клапаном. Полог со сматывающим устройством.
+Грузоподъёмность 37 000 кг, снаряжённая масса 10 000 кг, максимальная масса 47 000 кг. Нагрузка на оси 32 000 кг, на седло 15 000 кг. Внутренние размеры кузова 10 200×2 330×2 000 мм, объём кузова 44 м³. Погрузочная высота 1 450 мм, высота седельно-сцепного устройства 1 150–1 250 мм.
+Инструментальный ящик Daken, рукомойник Lokhen (Италия), 2 корзины запасного колеса.
+Гарантия 24 месяца без ограничения пробега. Комплектующие — BPW, JOST, Ermax, Binotto, Camozzi, AKKAR.</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
@@ -804,14 +805,14 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>1890000</t>
+          <t>2990000</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853372-halfpipe/11.jpg</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr"/>
@@ -841,7 +842,7 @@
       <c r="AA2" s="1" t="inlineStr"/>
       <c r="AB2" s="1" t="inlineStr">
         <is>
-          <t>1890000</t>
+          <t>2990000</t>
         </is>
       </c>
       <c r="AC2" s="1" t="inlineStr">
@@ -860,7 +861,7 @@
       <c r="AL2" s="1" t="inlineStr"/>
       <c r="AM2" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN2" s="1" t="inlineStr"/>
@@ -876,7 +877,7 @@
       </c>
       <c r="AQ2" s="1" t="inlineStr">
         <is>
-          <t>853375</t>
+          <t>853372</t>
         </is>
       </c>
       <c r="AR2" s="1" t="inlineStr">
@@ -886,19 +887,15 @@
       </c>
       <c r="AS2" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AT2" s="1" t="inlineStr"/>
       <c r="AU2" s="1" t="inlineStr"/>
-      <c r="AV2" s="1" t="inlineStr">
-        <is>
-          <t>EAR853375R0000773</t>
-        </is>
-      </c>
+      <c r="AV2" s="1" t="inlineStr"/>
       <c r="AW2" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX2" s="1" t="inlineStr">
@@ -913,20 +910,24 @@
       </c>
       <c r="AZ2" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA2" s="1" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>37000</t>
         </is>
       </c>
       <c r="BB2" s="1" t="inlineStr">
         <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="BC2" s="1" t="inlineStr"/>
+          <t>11200</t>
+        </is>
+      </c>
+      <c r="BC2" s="1" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="BD2" s="1" t="inlineStr"/>
       <c r="BE2" s="1" t="inlineStr"/>
     </row>
@@ -940,7 +941,7 @@
       <c r="C3" s="1" t="inlineStr"/>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-iso-xx246877</t>
+          <t>interpricep-853375-r0000773</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr"/>
@@ -957,14 +958,11 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп изотермический Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска пневматическая, тормоза барабанные.
-Грузоподъёмность 31 290 кг.
-Длина кузова 13,7 м, объём 94 м³.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Возможна аренда — уточняйте условия по телефону.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
+          <t>Полуприцеп-контейнеровоз ИнтерПрицеп 853375, 2024 год, в работе, полностью исправен.
+4 оси (3 + выносная балансирная), тормоза дисковые, ABS SORL. Подвеска пневматическая, с функцией подъёма осей — меньше износ резины на порожняке и разворотах. Шины 385/55R22.5, комплект 8+1 запасное.
+Берёт контейнеры 20', 30', 40' и High Cube — под большинство стандартных грузоперевозок без переоборудования. Разрешённая максимальная масса 47 000 кг, грузоподъёмность 41 000 кг. Высота погрузки 1 100 мм.
+Инструментальный ящик Daken, полный комплект пневморазводки и ЭБС.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
@@ -974,14 +972,14 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>4850000</t>
+          <t>1890000</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-09.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/interpricep-853375-r0000773/06.jpg</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr"/>
@@ -1011,7 +1009,7 @@
       <c r="AA3" s="1" t="inlineStr"/>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>4850000</t>
+          <t>1890000</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
@@ -1041,12 +1039,12 @@
       </c>
       <c r="AP3" s="1" t="inlineStr">
         <is>
-          <t>Kassbohrer</t>
+          <t>ИнтерПрицеп</t>
         </is>
       </c>
       <c r="AQ3" s="1" t="inlineStr">
         <is>
-          <t>Maxima</t>
+          <t>853375</t>
         </is>
       </c>
       <c r="AR3" s="1" t="inlineStr">
@@ -1056,24 +1054,24 @@
       </c>
       <c r="AS3" s="1" t="inlineStr">
         <is>
-          <t>Изотермический</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT3" s="1" t="inlineStr"/>
       <c r="AU3" s="1" t="inlineStr"/>
       <c r="AV3" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF10300124805</t>
+          <t>EAR853375R0000773</t>
         </is>
       </c>
       <c r="AW3" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX3" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY3" s="1" t="inlineStr">
@@ -1083,24 +1081,20 @@
       </c>
       <c r="AZ3" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA3" s="1" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="BB3" s="1" t="inlineStr">
         <is>
-          <t>13700</t>
-        </is>
-      </c>
-      <c r="BC3" s="1" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="BC3" s="1" t="inlineStr"/>
       <c r="BD3" s="1" t="inlineStr"/>
       <c r="BE3" s="1" t="inlineStr"/>
     </row>
@@ -1114,7 +1108,7 @@
       <c r="C4" s="1" t="inlineStr"/>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-shtor-00116344</t>
+          <t>kassbohrer-maxima-iso-xx246877</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
@@ -1131,14 +1125,13 @@
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer Maxima, 2022 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
-Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
-Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
-Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
+          <t>Полуприцеп изотермический Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска пневматическая, тормоза барабанные.
+Грузоподъёмность 31 290 кг.
+Длина кузова 13,7 м, объём 94 м³.
 Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
 Документы в порядке.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.
+Возможна аренда — уточняйте условия по телефону.
 Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
@@ -1149,14 +1142,14 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>4850000</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-iso-xx246877/r2-09.jpg</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>
@@ -1186,7 +1179,7 @@
       <c r="AA4" s="1" t="inlineStr"/>
       <c r="AB4" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>4850000</t>
         </is>
       </c>
       <c r="AC4" s="1" t="inlineStr">
@@ -1231,19 +1224,19 @@
       </c>
       <c r="AS4" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Изотермический</t>
         </is>
       </c>
       <c r="AT4" s="1" t="inlineStr"/>
       <c r="AU4" s="1" t="inlineStr"/>
       <c r="AV4" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF30300116344</t>
+          <t>WKVDAF10300124805</t>
         </is>
       </c>
       <c r="AW4" s="1" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX4" s="1" t="inlineStr">
@@ -1253,27 +1246,27 @@
       </c>
       <c r="AY4" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ4" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA4" s="1" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="BB4" s="1" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="BC4" s="1" t="inlineStr">
         <is>
-          <t>110.6</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BD4" s="1" t="inlineStr"/>
@@ -1289,7 +1282,7 @@
       <c r="C5" s="1" t="inlineStr"/>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-shtor-00124397</t>
+          <t>kassbohrer-maxima-shtor-00116344</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
@@ -1306,7 +1299,7 @@
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2022 год выпуска, TIR-исполнение.
 Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
 Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
 Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
@@ -1324,14 +1317,14 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>3290000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-04.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00116344/r2-10.jpg</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr"/>
@@ -1361,7 +1354,7 @@
       <c r="AA5" s="1" t="inlineStr"/>
       <c r="AB5" s="1" t="inlineStr">
         <is>
-          <t>3290000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC5" s="1" t="inlineStr">
@@ -1413,12 +1406,12 @@
       <c r="AU5" s="1" t="inlineStr"/>
       <c r="AV5" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF30300124397</t>
+          <t>WKVDAF30300116344</t>
         </is>
       </c>
       <c r="AW5" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="AX5" s="1" t="inlineStr">
@@ -1464,7 +1457,7 @@
       <c r="C6" s="1" t="inlineStr"/>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kassbohrer-maxima-shtor-00124732</t>
+          <t>kassbohrer-maxima-shtor-00124397</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -1481,11 +1474,11 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторный Kassbohrer, 2023 год выпуска, TIR-исполнение.
-Оси BPW, 3 шт., подвеска рессорная, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
-Масса снаряжённого 7 630 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 39 000 кг.
-Внутренние размеры 13 600×2 480×2 700 мм, объём кузова 92 м³. Высота ССУ 1150 мм.
-Боковая обшивка из фанеры, пол — ламинированная фанера 30 мм.
+          <t>Полуприцеп шторный Kassbohrer Maxima, 2023 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска зависимая на продольных рычагах, тормоза дисковые. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Масса снаряжённого полуприцепа 8 960 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 37 500 кг.
+Внутренние размеры 16 520×2 480×2 700 мм, объём кузова 110,6 м³. Высота ССУ 1150 мм.
+Боковая обшивка из фанеры, пол — ламинированная фанера 27 мм.
 Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
 Документы в порядке.
 Возможна аренда с правом выкупа — уточняйте условия по телефону.
@@ -1499,14 +1492,14 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>3290000</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124397/r2-04.jpg</t>
         </is>
       </c>
       <c r="S6" s="1" t="inlineStr"/>
@@ -1536,7 +1529,7 @@
       <c r="AA6" s="1" t="inlineStr"/>
       <c r="AB6" s="1" t="inlineStr">
         <is>
-          <t>2890000</t>
+          <t>3290000</t>
         </is>
       </c>
       <c r="AC6" s="1" t="inlineStr">
@@ -1588,7 +1581,7 @@
       <c r="AU6" s="1" t="inlineStr"/>
       <c r="AV6" s="1" t="inlineStr">
         <is>
-          <t>WKVDAF30300124732</t>
+          <t>WKVDAF30300124397</t>
         </is>
       </c>
       <c r="AW6" s="1" t="inlineStr">
@@ -1608,7 +1601,7 @@
       </c>
       <c r="AZ6" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA6" s="1" t="inlineStr">
@@ -1618,12 +1611,12 @@
       </c>
       <c r="BB6" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="BC6" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>110.6</t>
         </is>
       </c>
       <c r="BD6" s="1" t="inlineStr"/>
@@ -1639,7 +1632,7 @@
       <c r="C7" s="1" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pf41n-v000319</t>
+          <t>kassbohrer-maxima-shtor-00124732</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -1656,12 +1649,15 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Steelbear PF-41N (коммерческое название PF-41N FOX INTRA DISK), 4-х осный, универсал, под заказ.
-Перевозит 1×40-футовый контейнер (в т.ч. HQ), 2×20-футовых контейнера или 1×20-футовый по центру. Максимальная полная масса 47 000 кг, грузоподъёмность 41 100 кг, длина 12 600 мм.
-Осевой агрегат FOX B9-22S с дисковыми тормозами, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска FOX INTRA с подъёмом/опусканием 1-й оси (ручное управление) и 2-й оси (автоматическое). Электронная тормозная система Haldex EBS 4S/2M с функцией противоопрокидывания (RSS), информационная система INFOCENTER.
-Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая защита, заднее защитное устройство. Два инструментальных ящика SKARB с замком. Шины TYREX 385/55R22,5 на дисках KRONPRINZ, 9 колёс в комплекте (включая запасное).
-При покупке в лизинг — скидка от Минпромторга 10%.
-Заводская гарантия — 12 месяцев. Поставка — 10 рабочих дней с момента предоплаты.</t>
+          <t>Полуприцеп шторный Kassbohrer, 2023 год выпуска, TIR-исполнение.
+Оси BPW, 3 шт., подвеска рессорная, тормоза барабанные. Шины бескамерные 385/65R22,5, односкат, Bridgestone.
+Масса снаряжённого 7 630 кг, грузоподъёмность 28 540 кг, разрешённая максимальная масса 39 000 кг.
+Внутренние размеры 13 600×2 480×2 700 мм, объём кузова 92 м³. Высота ССУ 1150 мм.
+Боковая обшивка из фанеры, пол — ламинированная фанера 30 мм.
+Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
+Документы в порядке.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.
+Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
@@ -1671,14 +1667,14 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>3250000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/15.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/kassbohrer-maxima-shtor-00124732/r2-06.jpg</t>
         </is>
       </c>
       <c r="S7" s="1" t="inlineStr"/>
@@ -1708,19 +1704,15 @@
       <c r="AA7" s="1" t="inlineStr"/>
       <c r="AB7" s="1" t="inlineStr">
         <is>
-          <t>3250000</t>
+          <t>2890000</t>
         </is>
       </c>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="AD7" s="1" t="inlineStr">
-        <is>
-          <t>325000</t>
-        </is>
-      </c>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD7" s="1" t="inlineStr"/>
       <c r="AE7" s="1" t="inlineStr"/>
       <c r="AF7" s="1" t="inlineStr"/>
       <c r="AG7" s="1" t="inlineStr"/>
@@ -1731,7 +1723,7 @@
       <c r="AL7" s="1" t="inlineStr"/>
       <c r="AM7" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN7" s="1" t="inlineStr"/>
@@ -1742,12 +1734,12 @@
       </c>
       <c r="AP7" s="1" t="inlineStr">
         <is>
-          <t>Steelbear</t>
+          <t>Kassbohrer</t>
         </is>
       </c>
       <c r="AQ7" s="1" t="inlineStr">
         <is>
-          <t>PF-41N</t>
+          <t>Maxima</t>
         </is>
       </c>
       <c r="AR7" s="1" t="inlineStr">
@@ -1757,43 +1749,51 @@
       </c>
       <c r="AS7" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Шторный</t>
         </is>
       </c>
       <c r="AT7" s="1" t="inlineStr"/>
       <c r="AU7" s="1" t="inlineStr"/>
-      <c r="AV7" s="1" t="inlineStr"/>
+      <c r="AV7" s="1" t="inlineStr">
+        <is>
+          <t>WKVDAF30300124732</t>
+        </is>
+      </c>
       <c r="AW7" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX7" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY7" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ7" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA7" s="1" t="inlineStr">
         <is>
-          <t>41100</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="BB7" s="1" t="inlineStr">
         <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="BC7" s="1" t="inlineStr"/>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC7" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="BD7" s="1" t="inlineStr"/>
       <c r="BE7" s="1" t="inlineStr"/>
     </row>
@@ -1807,7 +1807,7 @@
       <c r="C8" s="1" t="inlineStr"/>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-avg36</t>
+          <t>steelbear-pf41n-v000319</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -1824,13 +1824,12 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L AVG), 3-х осный, под заказ.
-Осевой агрегат AVG Axle, квадратная ось сечением 120×120 мм — устойчивее к скручиванию на дорогах с боковым уклоном, чем круглая. Барабанные тормоза, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска AVG с подъёмом/опусканием. Электронная тормозная система TEBS 2S/2M с функцией противоопрокидывания (RSS), манометр давления в пневмоподвеске.
-6 пар коников с неоткрепляемыми стойками, грузоподъёмность 7 тонн каждая, положение регулируется вдоль рамы. Внутренняя высота коника 2 340 мм. 6 ремней для крепления сортимента. Неразборная передняя стенка перфорированного типа с крюками для каната и креплением для лома и лопаты.
-Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая противоподкатная защита. Металлический инструментальный ящик с замком. Шины TYREX 385/65R22,5.
-Максимальная полная масса 44 000 кг, грузоподъёмность 36 500 кг, длина 13 620 мм.
+          <t>Полуприцеп-контейнеровоз Steelbear PF-41N (коммерческое название PF-41N FOX INTRA DISK), 4-х осный, универсал, под заказ.
+Перевозит 1×40-футовый контейнер (в т.ч. HQ), 2×20-футовых контейнера или 1×20-футовый по центру. Максимальная полная масса 47 000 кг, грузоподъёмность 41 100 кг, длина 12 600 мм.
+Осевой агрегат FOX B9-22S с дисковыми тормозами, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска FOX INTRA с подъёмом/опусканием 1-й оси (ручное управление) и 2-й оси (автоматическое). Электронная тормозная система Haldex EBS 4S/2M с функцией противоопрокидывания (RSS), информационная система INFOCENTER.
+Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая защита, заднее защитное устройство. Два инструментальных ящика SKARB с замком. Шины TYREX 385/55R22,5 на дисках KRONPRINZ, 9 колёс в комплекте (включая запасное).
 При покупке в лизинг — скидка от Минпромторга 10%.
-Заводская гарантия — 12 месяцев. Поставка — 15 рабочих дней с момента предоплаты.</t>
+Заводская гарантия — 12 месяцев. Поставка — 10 рабочих дней с момента предоплаты.</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
@@ -1840,14 +1839,14 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>2960000</t>
+          <t>3250000</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/09.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pf41n-v000319/15.jpg</t>
         </is>
       </c>
       <c r="S8" s="1" t="inlineStr"/>
@@ -1877,7 +1876,7 @@
       <c r="AA8" s="1" t="inlineStr"/>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>2960000</t>
+          <t>3250000</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
@@ -1887,7 +1886,7 @@
       </c>
       <c r="AD8" s="1" t="inlineStr">
         <is>
-          <t>296000</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="AE8" s="1" t="inlineStr"/>
@@ -1916,7 +1915,7 @@
       </c>
       <c r="AQ8" s="1" t="inlineStr">
         <is>
-          <t>PL-24L</t>
+          <t>PF-41N</t>
         </is>
       </c>
       <c r="AR8" s="1" t="inlineStr">
@@ -1926,7 +1925,7 @@
       </c>
       <c r="AS8" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT8" s="1" t="inlineStr"/>
@@ -1939,7 +1938,7 @@
       </c>
       <c r="AX8" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY8" s="1" t="inlineStr">
@@ -1949,17 +1948,17 @@
       </c>
       <c r="AZ8" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA8" s="1" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>41100</t>
         </is>
       </c>
       <c r="BB8" s="1" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="BC8" s="1" t="inlineStr"/>
@@ -1976,7 +1975,7 @@
       <c r="C9" s="1" t="inlineStr"/>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>steelbear-pl24l-ea653666</t>
+          <t>steelbear-pl24l-avg36</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -1993,13 +1992,13 @@
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L SAF Heavy Duty), 2024 год выпуска, б/у, в наличии.
-Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
-6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
-Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
-Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
-Документы в порядке.
-Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L Fox), 3-х осный, под заказ.
+Осевой агрегат Fox, барабанные тормоза, допустимая нагрузка на ось 9 000 кг. Усиленная пневмоподвеска с подъёмом/опусканием. Электронная тормозная система TEBS 2S/2M с функцией противоопрокидывания (RSS), манометр давления в пневмоподвеске.
+6 пар коников с неоткрепляемыми стойками, грузоподъёмность 7 тонн каждая, положение регулируется вдоль рамы. Внутренняя высота коника 2 340 мм. 6 ремней для крепления сортимента. Неразборная передняя стенка перфорированного типа с крюками для каната и креплением для лома и лопаты.
+Опорное устройство GOS, 24 т, шкворень OREX 2 дюйма. Боковая алюминиевая противоподкатная защита. Металлический инструментальный ящик с замком. Шины TYREX 385/65R22,5.
+Максимальная полная масса 44 000 кг, грузоподъёмность 36 500 кг, длина 13 620 мм.
+При покупке в лизинг — скидка от Минпромторга 10%.
+Заводская гарантия — 12 месяцев. Поставка — 15 рабочих дней с момента предоплаты.</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
@@ -2009,14 +2008,14 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>2960000</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-avg36/09.jpg</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr"/>
@@ -2046,15 +2045,19 @@
       <c r="AA9" s="1" t="inlineStr"/>
       <c r="AB9" s="1" t="inlineStr">
         <is>
-          <t>2970000</t>
+          <t>2960000</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD9" s="1" t="inlineStr"/>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD9" s="1" t="inlineStr">
+        <is>
+          <t>296000</t>
+        </is>
+      </c>
       <c r="AE9" s="1" t="inlineStr"/>
       <c r="AF9" s="1" t="inlineStr"/>
       <c r="AG9" s="1" t="inlineStr"/>
@@ -2065,7 +2068,7 @@
       <c r="AL9" s="1" t="inlineStr"/>
       <c r="AM9" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN9" s="1" t="inlineStr"/>
@@ -2096,14 +2099,10 @@
       </c>
       <c r="AT9" s="1" t="inlineStr"/>
       <c r="AU9" s="1" t="inlineStr"/>
-      <c r="AV9" s="1" t="inlineStr">
-        <is>
-          <t>XWZ9412LLR1202021</t>
-        </is>
-      </c>
+      <c r="AV9" s="1" t="inlineStr"/>
       <c r="AW9" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX9" s="1" t="inlineStr">
@@ -2123,7 +2122,7 @@
       </c>
       <c r="BA9" s="1" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="BB9" s="1" t="inlineStr">
@@ -2145,7 +2144,7 @@
       <c r="C10" s="1" t="inlineStr"/>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>tonar-b313-9888</t>
+          <t>steelbear-pl24l-ea653666</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -2162,12 +2161,13 @@
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины на порожняке. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 150 000 ₽.
-Скидка от производителя на линейку бортовых прицепов (10%): −315 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −315 000 ₽.
-Итоговая цена при лизинге: 2 520 000 ₽.
-Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+          <t>Полуприцеп-сортиментовоз Steelbear PL-24L (коммерческое название PT-24L SAF Heavy Duty), 2024 год выпуска, б/у, в наличии.
+Усиленное шасси из двутавровых лонжеронов, 3 оси SAF Heavy Duty, барабанные тормоза, пневмоподвеска с функцией подъём/опускание, допустимая нагрузка на ось 9 000 кг. Шины 385/65R22,5, односкат. Электронная тормозная система WABCO TEBS-E с функцией противоопрокидывания (RSS).
+6 пар открепляемых коников грузоподъёмностью 8 тонн каждая (сталь STRENX 700MC), положение регулируется вдоль рамы. Внутренняя высота коника 2330 мм. Настил из ламинированной берёзовой фанеры. Опорное устройство BPW, 24 т.
+Максимальная полная масса 44 000 кг, грузоподъёмность 37 100 кг, длина 13 620 мм.
+Техническое состояние — на ходу, полностью исправен, не требует вложений и ремонта.
+Документы в порядке.
+Смотровая площадка и показ — по договорённости. Торг при осмотре.</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
@@ -2177,14 +2177,14 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>3150000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/steelbear-pl24l-ea653666/12.jpg</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr"/>
@@ -2214,25 +2214,17 @@
       <c r="AA10" s="1" t="inlineStr"/>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>3150000</t>
+          <t>2970000</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="AD10" s="1" t="inlineStr">
-        <is>
-          <t>315000</t>
-        </is>
-      </c>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD10" s="1" t="inlineStr"/>
       <c r="AE10" s="1" t="inlineStr"/>
-      <c r="AF10" s="1" t="inlineStr">
-        <is>
-          <t>315000</t>
-        </is>
-      </c>
+      <c r="AF10" s="1" t="inlineStr"/>
       <c r="AG10" s="1" t="inlineStr"/>
       <c r="AH10" s="1" t="inlineStr"/>
       <c r="AI10" s="1" t="inlineStr"/>
@@ -2241,7 +2233,7 @@
       <c r="AL10" s="1" t="inlineStr"/>
       <c r="AM10" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN10" s="1" t="inlineStr"/>
@@ -2252,12 +2244,12 @@
       </c>
       <c r="AP10" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>Steelbear</t>
         </is>
       </c>
       <c r="AQ10" s="1" t="inlineStr">
         <is>
-          <t>B3-13 (9888)</t>
+          <t>PL-24L</t>
         </is>
       </c>
       <c r="AR10" s="1" t="inlineStr">
@@ -2267,15 +2259,19 @@
       </c>
       <c r="AS10" s="1" t="inlineStr">
         <is>
-          <t>Бортовой</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT10" s="1" t="inlineStr"/>
       <c r="AU10" s="1" t="inlineStr"/>
-      <c r="AV10" s="1" t="inlineStr"/>
+      <c r="AV10" s="1" t="inlineStr">
+        <is>
+          <t>XWZ9412LLR1202021</t>
+        </is>
+      </c>
       <c r="AW10" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX10" s="1" t="inlineStr">
@@ -2295,12 +2291,12 @@
       </c>
       <c r="BA10" s="1" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="BB10" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="BC10" s="1" t="inlineStr"/>
@@ -2317,7 +2313,7 @@
       <c r="C11" s="1" t="inlineStr"/>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>tonar-k4u-99891-order</t>
+          <t>tonar-b313-9888</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -2334,13 +2330,12 @@
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 4 оси, вынесенная вперёд передняя ось на 2560 мм — меньше нагрузка на дорогу. ССУ=1100 мм, шины 385/55-R22.5. Берёт контейнеры 1×20', 2×20', 1×30', 1×40' High Cube. Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
-Скидка от производителя на линейку контейнеровозов (5%): −160 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
-Итоговая цена при лизинге: 2 720 000 ₽.
-Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.
-(У нас также есть эта же модель б/у, в наличии, дешевле — уточняйте по телефону, если новый под заказ не подходит по срокам.)</t>
+          <t>Полуприцеп бортовой Тонар B3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная — меньше износ резины на порожняке. ССУ 1200 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 150 000 ₽.
+Скидка от производителя на линейку бортовых прицепов (10%): −315 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −315 000 ₽.
+Итоговая цена при лизинге: 2 520 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -2350,14 +2345,14 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>3150000</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-b313-9888/10.jpg</t>
         </is>
       </c>
       <c r="S11" s="1" t="inlineStr"/>
@@ -2387,7 +2382,7 @@
       <c r="AA11" s="1" t="inlineStr"/>
       <c r="AB11" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>3150000</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
@@ -2397,13 +2392,13 @@
       </c>
       <c r="AD11" s="1" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>315000</t>
         </is>
       </c>
       <c r="AE11" s="1" t="inlineStr"/>
       <c r="AF11" s="1" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>315000</t>
         </is>
       </c>
       <c r="AG11" s="1" t="inlineStr"/>
@@ -2430,7 +2425,7 @@
       </c>
       <c r="AQ11" s="1" t="inlineStr">
         <is>
-          <t>K4-U (99891)</t>
+          <t>B3-13 (9888)</t>
         </is>
       </c>
       <c r="AR11" s="1" t="inlineStr">
@@ -2440,7 +2435,7 @@
       </c>
       <c r="AS11" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Бортовой</t>
         </is>
       </c>
       <c r="AT11" s="1" t="inlineStr"/>
@@ -2453,7 +2448,7 @@
       </c>
       <c r="AX11" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY11" s="1" t="inlineStr">
@@ -2468,12 +2463,12 @@
       </c>
       <c r="BA11" s="1" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>31600</t>
         </is>
       </c>
       <c r="BB11" s="1" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="BC11" s="1" t="inlineStr"/>
@@ -2490,7 +2485,7 @@
       <c r="C12" s="1" t="inlineStr"/>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>tonar-k4u-p0002033</t>
+          <t>tonar-k4u-99891-order</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
@@ -2507,10 +2502,13 @@
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
-4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
-Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 4 оси, вынесенная вперёд передняя ось на 2560 мм — меньше нагрузка на дорогу. ССУ=1100 мм, шины 385/55-R22.5. Берёт контейнеры 1×20', 2×20', 1×30', 1×40' High Cube. Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
+Скидка от производителя на линейку контейнеровозов (5%): −160 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
+Итоговая цена при лизинге: 2 720 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.
+(У нас также есть эта же модель б/у, в наличии, дешевле — уточняйте по телефону, если новый под заказ не подходит по срокам.)</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
@@ -2520,14 +2518,14 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
       <c r="R12" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-99891-order/10.jpg</t>
         </is>
       </c>
       <c r="S12" s="1" t="inlineStr"/>
@@ -2557,17 +2555,25 @@
       <c r="AA12" s="1" t="inlineStr"/>
       <c r="AB12" s="1" t="inlineStr">
         <is>
-          <t>1690000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="AC12" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD12" s="1" t="inlineStr"/>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD12" s="1" t="inlineStr">
+        <is>
+          <t>320000</t>
+        </is>
+      </c>
       <c r="AE12" s="1" t="inlineStr"/>
-      <c r="AF12" s="1" t="inlineStr"/>
+      <c r="AF12" s="1" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
       <c r="AG12" s="1" t="inlineStr"/>
       <c r="AH12" s="1" t="inlineStr"/>
       <c r="AI12" s="1" t="inlineStr"/>
@@ -2576,7 +2582,7 @@
       <c r="AL12" s="1" t="inlineStr"/>
       <c r="AM12" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN12" s="1" t="inlineStr"/>
@@ -2607,14 +2613,10 @@
       </c>
       <c r="AT12" s="1" t="inlineStr"/>
       <c r="AU12" s="1" t="inlineStr"/>
-      <c r="AV12" s="1" t="inlineStr">
-        <is>
-          <t>X0T998910P0002033</t>
-        </is>
-      </c>
+      <c r="AV12" s="1" t="inlineStr"/>
       <c r="AW12" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX12" s="1" t="inlineStr">
@@ -2624,12 +2626,12 @@
       </c>
       <c r="AY12" s="1" t="inlineStr">
         <is>
-          <t>Рессорная</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AZ12" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA12" s="1" t="inlineStr">
@@ -2639,7 +2641,7 @@
       </c>
       <c r="BB12" s="1" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="BC12" s="1" t="inlineStr"/>
@@ -2656,7 +2658,7 @@
       <c r="C13" s="1" t="inlineStr"/>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>tonar-l3-9445</t>
+          <t>tonar-k4u-p0002033</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr"/>
@@ -2673,12 +2675,10 @@
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ на порожняке. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
-Скидка от производителя на линейку лесовозов (5%): −160 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
-Итоговая цена при лизинге: 2 720 000 ₽.
-Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
+          <t>Полуприцеп-контейнеровоз Тонар К4-U (99891), 2023 год, в работе, полностью исправен.
+4 оси: тройная задняя тележка плюс вынесенная вперёд ось — меньше нагрузка на дорогу и мягче по осевым ограничениям в городе. Тормоза дисковые, пневмопривод. Подвеска зависимая, на продольных рычагах, с пневмоэлементами и телескопическими амортизаторами. Шины 385/55R22.5, односкатные.
+Берёт контейнеры 20', 2×20', 30', 30' HC, 40', 40' HC. Разрешённая максимальная масса 44 000 кг, грузоподъёмность 37 800 кг, нагрузка на ССУ 11 000 кг. Высота ССУ 1 100 мм.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -2688,14 +2688,14 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-k4u-p0002033/08.jpg</t>
         </is>
       </c>
       <c r="S13" s="1" t="inlineStr"/>
@@ -2725,25 +2725,17 @@
       <c r="AA13" s="1" t="inlineStr"/>
       <c r="AB13" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>1690000</t>
         </is>
       </c>
       <c r="AC13" s="1" t="inlineStr">
         <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
-          <t>320000</t>
-        </is>
-      </c>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD13" s="1" t="inlineStr"/>
       <c r="AE13" s="1" t="inlineStr"/>
-      <c r="AF13" s="1" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
+      <c r="AF13" s="1" t="inlineStr"/>
       <c r="AG13" s="1" t="inlineStr"/>
       <c r="AH13" s="1" t="inlineStr"/>
       <c r="AI13" s="1" t="inlineStr"/>
@@ -2752,7 +2744,7 @@
       <c r="AL13" s="1" t="inlineStr"/>
       <c r="AM13" s="1" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>С пробегом</t>
         </is>
       </c>
       <c r="AN13" s="1" t="inlineStr"/>
@@ -2768,7 +2760,7 @@
       </c>
       <c r="AQ13" s="1" t="inlineStr">
         <is>
-          <t>L3 (9445)</t>
+          <t>K4-U (99891)</t>
         </is>
       </c>
       <c r="AR13" s="1" t="inlineStr">
@@ -2778,47 +2770,47 @@
       </c>
       <c r="AS13" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AT13" s="1" t="inlineStr"/>
       <c r="AU13" s="1" t="inlineStr"/>
-      <c r="AV13" s="1" t="inlineStr"/>
+      <c r="AV13" s="1" t="inlineStr">
+        <is>
+          <t>X0T998910P0002033</t>
+        </is>
+      </c>
       <c r="AW13" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX13" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY13" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Рессорная</t>
         </is>
       </c>
       <c r="AZ13" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA13" s="1" t="inlineStr">
         <is>
-          <t>36700</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="BB13" s="1" t="inlineStr">
         <is>
-          <t>12800</t>
-        </is>
-      </c>
-      <c r="BC13" s="1" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="BC13" s="1" t="inlineStr"/>
       <c r="BD13" s="1" t="inlineStr"/>
       <c r="BE13" s="1" t="inlineStr"/>
     </row>
@@ -2832,7 +2824,7 @@
       <c r="C14" s="1" t="inlineStr"/>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>tonar-reef-r313</t>
+          <t>tonar-l3-9445</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr"/>
@@ -2849,11 +2841,11 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 85 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
-В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины (у нас в парке такой есть от 4 850 000 ₽ по прайсу завода без холодильной установки).
-Цена: 7 365 000 ₽ (на эту линейку скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 6 865 000 ₽.
+          <t>Полуприцеп-сортиментовоз Тонар L3 (9445), 3 оси, ССУ 1150/1250/1350 мм с подъёмной осью — меньше износ на порожняке. Коники разборные, 6 штук, межосевое расстояние 1310 мм, рычажная подвеска, барабанные тормоза. Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 200 000 ₽.
+Скидка от производителя на линейку лесовозов (5%): −160 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −320 000 ₽.
+Итоговая цена при лизинге: 2 720 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -2864,14 +2856,14 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>7365000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-l3-9445/10.jpg</t>
         </is>
       </c>
       <c r="S14" s="1" t="inlineStr"/>
@@ -2901,7 +2893,7 @@
       <c r="AA14" s="1" t="inlineStr"/>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>7365000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="AC14" s="1" t="inlineStr">
@@ -2911,11 +2903,15 @@
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="AE14" s="1" t="inlineStr"/>
-      <c r="AF14" s="1" t="inlineStr"/>
+      <c r="AF14" s="1" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
       <c r="AG14" s="1" t="inlineStr"/>
       <c r="AH14" s="1" t="inlineStr"/>
       <c r="AI14" s="1" t="inlineStr"/>
@@ -2940,7 +2936,7 @@
       </c>
       <c r="AQ14" s="1" t="inlineStr">
         <is>
-          <t>R3-13</t>
+          <t>L3 (9445)</t>
         </is>
       </c>
       <c r="AR14" s="1" t="inlineStr">
@@ -2950,7 +2946,7 @@
       </c>
       <c r="AS14" s="1" t="inlineStr">
         <is>
-          <t>Рефрижератор</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AT14" s="1" t="inlineStr"/>
@@ -2973,22 +2969,22 @@
       </c>
       <c r="AZ14" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA14" s="1" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="BB14" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="BC14" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BD14" s="1" t="inlineStr"/>
@@ -3004,7 +3000,7 @@
       <c r="C15" s="1" t="inlineStr"/>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>tonar-samosval-9595</t>
+          <t>tonar-reef-r313</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr"/>
@@ -3021,10 +3017,11 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп самосвальный Тонар SH4-34 (9595) с задней разгрузкой, облегчённый, объём кузова 33,6 м³, четырёхосный, пневматическая рычажная подвеска, барабанные тормоза. Кузов полукруглой формы — сыпучий груз сходит легче, без залипания, в том числе влажный. Подходит под сыпучие строительные материалы. Тент с ручной намоткой в базе. Новое, под заказ у завода-изготовителя.
-Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
-Итоговая цена при лизинге: 3 780 000 ₽.
+          <t>Полуприцеп рефрижератор Тонар R3-13, 13,6 м, трёхосный, первая ось подъёмная, объём кузова 85 м³, дисковые оси, ССУ-1150 мм, вместимость 33 европаллеты. Новое, под заказ у завода-изготовителя.
+В отличие от обычного изотермического кузова (без активного охлаждения), этот прицеп доукомплектован новой холодильно-отопительной установкой (ХОУ) — держит заданную температуру в пути, не только теплоизолирует. Именно установка ХОУ и делает цену заметно выше базового изотермического кузова той же длины (у нас в парке такой есть от 4 850 000 ₽ по прайсу завода без холодильной установки).
+Цена: 7 365 000 ₽ (на эту линейку скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 6 865 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3035,14 +3032,14 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>4200000</t>
+          <t>7365000</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/03.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-reef-r313/06.jpg</t>
         </is>
       </c>
       <c r="S15" s="1" t="inlineStr"/>
@@ -3072,7 +3069,7 @@
       <c r="AA15" s="1" t="inlineStr"/>
       <c r="AB15" s="1" t="inlineStr">
         <is>
-          <t>4200000</t>
+          <t>7365000</t>
         </is>
       </c>
       <c r="AC15" s="1" t="inlineStr">
@@ -3082,7 +3079,7 @@
       </c>
       <c r="AD15" s="1" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AE15" s="1" t="inlineStr"/>
@@ -3111,7 +3108,7 @@
       </c>
       <c r="AQ15" s="1" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>R3-13</t>
         </is>
       </c>
       <c r="AR15" s="1" t="inlineStr">
@@ -3121,7 +3118,7 @@
       </c>
       <c r="AS15" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Рефрижератор</t>
         </is>
       </c>
       <c r="AT15" s="1" t="inlineStr"/>
@@ -3134,7 +3131,7 @@
       </c>
       <c r="AX15" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY15" s="1" t="inlineStr">
@@ -3144,18 +3141,22 @@
       </c>
       <c r="AZ15" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA15" s="1" t="inlineStr">
         <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="BB15" s="1" t="inlineStr"/>
+          <t>31200</t>
+        </is>
+      </c>
+      <c r="BB15" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
       <c r="BC15" s="1" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BD15" s="1" t="inlineStr"/>
@@ -3171,7 +3172,7 @@
       <c r="C16" s="1" t="inlineStr"/>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>tonar-sdp489-95895</t>
+          <t>tonar-samosval-9595</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr"/>
@@ -3188,11 +3189,10 @@
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп со сдвижными полами Тонар SDP4-89 (95895), 4 оси (первая вынесенная), габаритная длина 14,6 м, погрузочная длина 14,1 м, алюминиевый кузов, объём 89 м³, ССУ=1150 мм. Новое, под заказ у завода-изготовителя.
-Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без опрокидывания кузова — можно разгружаться на неровных площадках и под низкими навесами, где самосвал не встанет. Универсален под насыпные грузы: щепа, зерно, песок и т.п.
-Цена: 7 650 000 ₽ (на эту линейку скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 7 150 000 ₽.
+          <t>Полуприцеп самосвальный Тонар SH4-34 (9595) с задней разгрузкой, облегчённый, объём кузова 33,6 м³, четырёхосный, пневматическая рычажная подвеска, барабанные тормоза. Кузов полукруглой формы — сыпучий груз сходит легче, без залипания, в том числе влажный. Подходит под сыпучие строительные материалы. Тент с ручной намоткой в базе. Новое, под заказ у завода-изготовителя.
+Цена: 4 200 000 ₽ (на линейку самосвальных полуприцепов скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −420 000 ₽.
+Итоговая цена при лизинге: 3 780 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3203,14 +3203,14 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>7650000</t>
+          <t>4200000</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/03.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-samosval-9595/03.jpg</t>
         </is>
       </c>
       <c r="S16" s="1" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       <c r="AA16" s="1" t="inlineStr"/>
       <c r="AB16" s="1" t="inlineStr">
         <is>
-          <t>7650000</t>
+          <t>4200000</t>
         </is>
       </c>
       <c r="AC16" s="1" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="AD16" s="1" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="AE16" s="1" t="inlineStr"/>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AQ16" s="1" t="inlineStr">
         <is>
-          <t>SDP4-89 (95895)</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="AR16" s="1" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AS16" s="1" t="inlineStr">
         <is>
-          <t>Щеповоз</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AT16" s="1" t="inlineStr"/>
@@ -3312,22 +3312,18 @@
       </c>
       <c r="AZ16" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA16" s="1" t="inlineStr">
         <is>
-          <t>27800</t>
-        </is>
-      </c>
-      <c r="BB16" s="1" t="inlineStr">
-        <is>
-          <t>14600</t>
-        </is>
-      </c>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="BB16" s="1" t="inlineStr"/>
       <c r="BC16" s="1" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BD16" s="1" t="inlineStr"/>
@@ -3343,7 +3339,7 @@
       <c r="C17" s="1" t="inlineStr"/>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>tonar-t313-9888</t>
+          <t>tonar-sdp489-95895</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr"/>
@@ -3360,11 +3356,11 @@
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная, объём 91,4 м³. Дисковые оси, ССУ-1150 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
-Цена по действующему прайсу завода (с 27.07.2026): 3 800 000 ₽.
-Скидка от производителя на линейку шторных прицепов (10%): −380 000 ₽.
-При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −380 000 ₽.
-Итоговая цена при лизинге: 3 040 000 ₽.
+          <t>Полуприцеп со сдвижными полами Тонар SDP4-89 (95895), 4 оси (первая вынесенная), габаритная длина 14,6 м, погрузочная длина 14,1 м, алюминиевый кузов, объём 89 м³, ССУ=1150 мм. Новое, под заказ у завода-изготовителя.
+Сдвижной пол (Cargo Floor) выгружает груз горизонтально, без опрокидывания кузова — можно разгружаться на неровных площадках и под низкими навесами, где самосвал не встанет. Универсален под насыпные грузы: щепа, зерно, песок и т.п.
+Цена: 7 650 000 ₽ (на эту линейку скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 7 150 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3375,14 +3371,14 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>3800000</t>
+          <t>7650000</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/10.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-sdp489-95895/03.jpg</t>
         </is>
       </c>
       <c r="S17" s="1" t="inlineStr"/>
@@ -3412,7 +3408,7 @@
       <c r="AA17" s="1" t="inlineStr"/>
       <c r="AB17" s="1" t="inlineStr">
         <is>
-          <t>3800000</t>
+          <t>7650000</t>
         </is>
       </c>
       <c r="AC17" s="1" t="inlineStr">
@@ -3422,15 +3418,11 @@
       </c>
       <c r="AD17" s="1" t="inlineStr">
         <is>
-          <t>380000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AE17" s="1" t="inlineStr"/>
-      <c r="AF17" s="1" t="inlineStr">
-        <is>
-          <t>380000</t>
-        </is>
-      </c>
+      <c r="AF17" s="1" t="inlineStr"/>
       <c r="AG17" s="1" t="inlineStr"/>
       <c r="AH17" s="1" t="inlineStr"/>
       <c r="AI17" s="1" t="inlineStr"/>
@@ -3455,7 +3447,7 @@
       </c>
       <c r="AQ17" s="1" t="inlineStr">
         <is>
-          <t>T3-13 (9888)</t>
+          <t>SDP4-89 (95895)</t>
         </is>
       </c>
       <c r="AR17" s="1" t="inlineStr">
@@ -3465,7 +3457,7 @@
       </c>
       <c r="AS17" s="1" t="inlineStr">
         <is>
-          <t>Шторно-бортовой</t>
+          <t>Щеповоз</t>
         </is>
       </c>
       <c r="AT17" s="1" t="inlineStr"/>
@@ -3478,7 +3470,7 @@
       </c>
       <c r="AX17" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY17" s="1" t="inlineStr">
@@ -3493,17 +3485,17 @@
       </c>
       <c r="BA17" s="1" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>27800</t>
         </is>
       </c>
       <c r="BB17" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="BC17" s="1" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD17" s="1" t="inlineStr"/>
@@ -3519,7 +3511,7 @@
       <c r="C18" s="1" t="inlineStr"/>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>tonar-zernovoz-95941</t>
+          <t>tonar-t313-9888</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr"/>
@@ -3536,10 +3528,11 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый кузов прямоугольной формы, объём 50 м³, до 31 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными люками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
-Цена: 5 400 000 ₽ (на линейку зерновозов скидка от производителя не действует).
-При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
-Итоговая цена при лизинге: 4 900 000 ₽.
+          <t>Полуприцеп шторно-бортовой Тонар T3-13 (9888), 13,6 м, трёхосный, первая ось подъёмная, объём 91,4 м³. Дисковые оси, ССУ-1150 мм, со стаканами под коники (коники в комплект не входят). Новое, под заказ у завода-изготовителя.
+Цена по действующему прайсу завода (с 27.07.2026): 3 800 000 ₽.
+Скидка от производителя на линейку шторных прицепов (10%): −380 000 ₽.
+При покупке в лизинг — дополнительная субсидия от Минпромторга (10%, не более 500 000 ₽): −380 000 ₽.
+Итоговая цена при лизинге: 3 040 000 ₽.
 Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
@@ -3550,14 +3543,14 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>5400000</t>
+          <t>3800000</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr"/>
       <c r="R18" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/05.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-t313-9888/10.jpg</t>
         </is>
       </c>
       <c r="S18" s="1" t="inlineStr"/>
@@ -3587,7 +3580,7 @@
       <c r="AA18" s="1" t="inlineStr"/>
       <c r="AB18" s="1" t="inlineStr">
         <is>
-          <t>5400000</t>
+          <t>3800000</t>
         </is>
       </c>
       <c r="AC18" s="1" t="inlineStr">
@@ -3597,11 +3590,15 @@
       </c>
       <c r="AD18" s="1" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>380000</t>
         </is>
       </c>
       <c r="AE18" s="1" t="inlineStr"/>
-      <c r="AF18" s="1" t="inlineStr"/>
+      <c r="AF18" s="1" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
       <c r="AG18" s="1" t="inlineStr"/>
       <c r="AH18" s="1" t="inlineStr"/>
       <c r="AI18" s="1" t="inlineStr"/>
@@ -3626,7 +3623,7 @@
       </c>
       <c r="AQ18" s="1" t="inlineStr">
         <is>
-          <t>95941</t>
+          <t>T3-13 (9888)</t>
         </is>
       </c>
       <c r="AR18" s="1" t="inlineStr">
@@ -3636,7 +3633,7 @@
       </c>
       <c r="AS18" s="1" t="inlineStr">
         <is>
-          <t>Зерновоз</t>
+          <t>Шторно-бортовой</t>
         </is>
       </c>
       <c r="AT18" s="1" t="inlineStr"/>
@@ -3659,7 +3656,7 @@
       </c>
       <c r="AZ18" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA18" s="1" t="inlineStr">
@@ -3667,10 +3664,14 @@
           <t>31000</t>
         </is>
       </c>
-      <c r="BB18" s="1" t="inlineStr"/>
+      <c r="BB18" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
       <c r="BC18" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD18" s="1" t="inlineStr"/>
@@ -3686,7 +3687,7 @@
       <c r="C19" s="1" t="inlineStr"/>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>tverstroymash-993941-0al4980</t>
+          <t>tonar-zernovoz-95941</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr"/>
@@ -3703,12 +3704,11 @@
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-тяжеловоз (трал) Тверьстроймаш 993941, исполнение RL40GW (серия Rapid), 2024 год, в наличии.
-4 оси (3+1): 1-я стационарная подъёмная, 2-я и 3-я стационарные, 4-я подруливающая — подвеска пневматическая, тормоза барабанные с АБС. Шины 235/75 R17.5, Кама.
-Грузоподъёмность технически допустимая 40 000 кг, нагрузка на ССУ тягача 15 000 кг. Раздвижная грузовая платформа (гусёк) — длина при полном раздвижении 10 790 мм, ширина 2530 мм (с уширителями до 2990 мм), высота погрузки 890 мм. Настил платформы — дерево с металлическим профилем, на гуське — дерево.
-В комплекте: 2 запасных колеса с системой вертикальной установки, 4 аппарели (Тверьстроймаш, 45 т, ручные), уширители грузовой платформы, комплект из 4 выдвижных знаков «Крупногабаритный груз» со светотехникой и стробоскопами, проблесковый маячок, система мониторинга осевых нагрузок (2 датчика) и манометры контроля на 4 оси, инструментальный ящик (480 л), комплект фитингов для контейнера 1×40', вставные стойки.
-Цвет красный (RAL 3020). Документы в порядке — СТС и спецификация на руках.
-Цена: 8 200 000 ₽.</t>
+          <t>Полуприцеп-зерновоз Тонар 95941 с задней разгрузкой, алюминиевый кузов прямоугольной формы, объём 50 м³, до 31 тонны груза. Тент с механическим приводом в базовой комплектации. Задний борт комбинированный (откидной и распашной), с разгрузочными люками. Подвеска рычажного типа с пневмоэлементами, 3 оси (первая подъёмная), тормозная система TEBS. Универсален — насыпные зерновые/комбикорм и паллетированный груз. Новое, под заказ у завода-изготовителя.
+Цена: 5 400 000 ₽ (на линейку зерновозов скидка от производителя не действует).
+При покупке в лизинг — субсидия от Минпромторга (10%, не более 500 000 ₽): −500 000 ₽.
+Итоговая цена при лизинге: 4 900 000 ₽.
+Заводская гарантия — 12 месяцев. Поставка после согласования комплектации.</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
@@ -3718,14 +3718,14 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>8200000</t>
+          <t>5400000</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr"/>
       <c r="R19" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tonar-zernovoz-95941/05.jpg</t>
         </is>
       </c>
       <c r="S19" s="1" t="inlineStr"/>
@@ -3755,15 +3755,19 @@
       <c r="AA19" s="1" t="inlineStr"/>
       <c r="AB19" s="1" t="inlineStr">
         <is>
-          <t>8200000</t>
+          <t>5400000</t>
         </is>
       </c>
       <c r="AC19" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD19" s="1" t="inlineStr"/>
+          <t>Под заказ</t>
+        </is>
+      </c>
+      <c r="AD19" s="1" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
       <c r="AE19" s="1" t="inlineStr"/>
       <c r="AF19" s="1" t="inlineStr"/>
       <c r="AG19" s="1" t="inlineStr"/>
@@ -3774,7 +3778,7 @@
       <c r="AL19" s="1" t="inlineStr"/>
       <c r="AM19" s="1" t="inlineStr">
         <is>
-          <t>С пробегом</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="AN19" s="1" t="inlineStr"/>
@@ -3785,12 +3789,12 @@
       </c>
       <c r="AP19" s="1" t="inlineStr">
         <is>
-          <t>Тверьстроймаш</t>
+          <t>Тонар</t>
         </is>
       </c>
       <c r="AQ19" s="1" t="inlineStr">
         <is>
-          <t>993941</t>
+          <t>95941</t>
         </is>
       </c>
       <c r="AR19" s="1" t="inlineStr">
@@ -3800,24 +3804,20 @@
       </c>
       <c r="AS19" s="1" t="inlineStr">
         <is>
-          <t>Трал (тяжеловоз)</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="AT19" s="1" t="inlineStr"/>
       <c r="AU19" s="1" t="inlineStr"/>
-      <c r="AV19" s="1" t="inlineStr">
-        <is>
-          <t>X89993940R0AL4980</t>
-        </is>
-      </c>
+      <c r="AV19" s="1" t="inlineStr"/>
       <c r="AW19" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AX19" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY19" s="1" t="inlineStr">
@@ -3832,15 +3832,15 @@
       </c>
       <c r="BA19" s="1" t="inlineStr">
         <is>
-          <t>40000</t>
-        </is>
-      </c>
-      <c r="BB19" s="1" t="inlineStr">
-        <is>
-          <t>10790</t>
-        </is>
-      </c>
-      <c r="BC19" s="1" t="inlineStr"/>
+          <t>31000</t>
+        </is>
+      </c>
+      <c r="BB19" s="1" t="inlineStr"/>
+      <c r="BC19" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="BD19" s="1" t="inlineStr"/>
       <c r="BE19" s="1" t="inlineStr"/>
     </row>
@@ -3854,7 +3854,7 @@
       <c r="C20" s="1" t="inlineStr"/>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>v-trailer-329d-r0000119</t>
+          <t>tverstroymash-993941-0al4980</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr"/>
@@ -3871,10 +3871,12 @@
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+          <t>Полуприцеп-тяжеловоз (трал) Тверьстроймаш 993941, исполнение RL40GW (серия Rapid), 2024 год, в наличии.
+4 оси (3+1): 1-я стационарная подъёмная, 2-я и 3-я стационарные, 4-я подруливающая — подвеска пневматическая, тормоза барабанные с АБС. Шины 235/75 R17.5, Кама.
+Грузоподъёмность технически допустимая 40 000 кг, нагрузка на ССУ тягача 15 000 кг. Раздвижная грузовая платформа (гусёк) — длина при полном раздвижении 10 790 мм, ширина 2530 мм (с уширителями до 2990 мм), высота погрузки 890 мм. Настил платформы — дерево с металлическим профилем, на гуське — дерево.
+В комплекте: 2 запасных колеса с системой вертикальной установки, 4 аппарели (Тверьстроймаш, 45 т, ручные), уширители грузовой платформы, комплект из 4 выдвижных знаков «Крупногабаритный груз» со светотехникой и стробоскопами, проблесковый маячок, система мониторинга осевых нагрузок (2 датчика) и манометры контроля на 4 оси, инструментальный ящик (480 л), комплект фитингов для контейнера 1×40', вставные стойки.
+Цвет красный (RAL 3020). Документы в порядке — СТС и спецификация на руках.
+Цена: 8 200 000 ₽.</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -3884,14 +3886,14 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>8200000</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
       <c r="Q20" s="1" t="inlineStr"/>
       <c r="R20" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/08.jpg</t>
         </is>
       </c>
       <c r="S20" s="1" t="inlineStr"/>
@@ -3921,7 +3923,7 @@
       <c r="AA20" s="1" t="inlineStr"/>
       <c r="AB20" s="1" t="inlineStr">
         <is>
-          <t>2990000</t>
+          <t>8200000</t>
         </is>
       </c>
       <c r="AC20" s="1" t="inlineStr">
@@ -3951,12 +3953,12 @@
       </c>
       <c r="AP20" s="1" t="inlineStr">
         <is>
-          <t>V-Trailer</t>
+          <t>Тверьстроймаш</t>
         </is>
       </c>
       <c r="AQ20" s="1" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>993941</t>
         </is>
       </c>
       <c r="AR20" s="1" t="inlineStr">
@@ -3966,24 +3968,24 @@
       </c>
       <c r="AS20" s="1" t="inlineStr">
         <is>
-          <t>Шторный</t>
+          <t>Трал (тяжеловоз)</t>
         </is>
       </c>
       <c r="AT20" s="1" t="inlineStr"/>
       <c r="AU20" s="1" t="inlineStr"/>
       <c r="AV20" s="1" t="inlineStr">
         <is>
-          <t>XZFVKRP3DR0000119</t>
+          <t>X89993940R0AL4980</t>
         </is>
       </c>
       <c r="AW20" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AX20" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY20" s="1" t="inlineStr">
@@ -3993,26 +3995,192 @@
       </c>
       <c r="AZ20" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
+          <t>Барабанные</t>
         </is>
       </c>
       <c r="BA20" s="1" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="BB20" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC20" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
+          <t>10790</t>
+        </is>
+      </c>
+      <c r="BC20" s="1" t="inlineStr"/>
       <c r="BD20" s="1" t="inlineStr"/>
       <c r="BE20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr"/>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>v-trailer-329d-r0000119</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+      <c r="G21" s="1" t="inlineStr"/>
+      <c r="H21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr"/>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>Грузовики и спецтехника</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="P21" s="1" t="inlineStr"/>
+      <c r="Q21" s="1" t="inlineStr"/>
+      <c r="R21" s="1" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
+        </is>
+      </c>
+      <c r="S21" s="1" t="inlineStr"/>
+      <c r="T21" s="1" t="inlineStr"/>
+      <c r="U21" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15с2</t>
+        </is>
+      </c>
+      <c r="V21" s="1" t="inlineStr"/>
+      <c r="W21" s="1" t="inlineStr"/>
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="Y21" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="Z21" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA21" s="1" t="inlineStr"/>
+      <c r="AB21" s="1" t="inlineStr">
+        <is>
+          <t>2990000</t>
+        </is>
+      </c>
+      <c r="AC21" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AD21" s="1" t="inlineStr"/>
+      <c r="AE21" s="1" t="inlineStr"/>
+      <c r="AF21" s="1" t="inlineStr"/>
+      <c r="AG21" s="1" t="inlineStr"/>
+      <c r="AH21" s="1" t="inlineStr"/>
+      <c r="AI21" s="1" t="inlineStr"/>
+      <c r="AJ21" s="1" t="inlineStr"/>
+      <c r="AK21" s="1" t="inlineStr"/>
+      <c r="AL21" s="1" t="inlineStr"/>
+      <c r="AM21" s="1" t="inlineStr">
+        <is>
+          <t>С пробегом</t>
+        </is>
+      </c>
+      <c r="AN21" s="1" t="inlineStr"/>
+      <c r="AO21" s="1" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="AP21" s="1" t="inlineStr">
+        <is>
+          <t>V-Trailer</t>
+        </is>
+      </c>
+      <c r="AQ21" s="1" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AR21" s="1" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AS21" s="1" t="inlineStr">
+        <is>
+          <t>Шторный</t>
+        </is>
+      </c>
+      <c r="AT21" s="1" t="inlineStr"/>
+      <c r="AU21" s="1" t="inlineStr"/>
+      <c r="AV21" s="1" t="inlineStr">
+        <is>
+          <t>XZFVKRP3DR0000119</t>
+        </is>
+      </c>
+      <c r="AW21" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AX21" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY21" s="1" t="inlineStr">
+        <is>
+          <t>Пневматическая</t>
+        </is>
+      </c>
+      <c r="AZ21" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
+      <c r="BA21" s="1" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="BB21" s="1" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC21" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="BD21" s="1" t="inlineStr"/>
+      <c r="BE21" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito-feed-trailers/fleet-trailers.xlsx
+++ b/avito-feed-trailers/fleet-trailers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE21"/>
+  <dimension ref="A1:BE20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,7 @@
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="25" customWidth="1" min="45" max="45"/>
@@ -3854,7 +3854,7 @@
       <c r="C20" s="1" t="inlineStr"/>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>tverstroymash-993941-0al4980</t>
+          <t>v-trailer-329d-r0000119</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr"/>
@@ -3871,12 +3871,10 @@
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп-тяжеловоз (трал) Тверьстроймаш 993941, исполнение RL40GW (серия Rapid), 2024 год, в наличии.
-4 оси (3+1): 1-я стационарная подъёмная, 2-я и 3-я стационарные, 4-я подруливающая — подвеска пневматическая, тормоза барабанные с АБС. Шины 235/75 R17.5, Кама.
-Грузоподъёмность технически допустимая 40 000 кг, нагрузка на ССУ тягача 15 000 кг. Раздвижная грузовая платформа (гусёк) — длина при полном раздвижении 10 790 мм, ширина 2530 мм (с уширителями до 2990 мм), высота погрузки 890 мм. Настил платформы — дерево с металлическим профилем, на гуське — дерево.
-В комплекте: 2 запасных колеса с системой вертикальной установки, 4 аппарели (Тверьстроймаш, 45 т, ручные), уширители грузовой платформы, комплект из 4 выдвижных знаков «Крупногабаритный груз» со светотехникой и стробоскопами, проблесковый маячок, система мониторинга осевых нагрузок (2 датчика) и манометры контроля на 4 оси, инструментальный ящик (480 л), комплект фитингов для контейнера 1×40', вставные стойки.
-Цвет красный (RAL 3020). Документы в порядке — СТС и спецификация на руках.
-Цена: 8 200 000 ₽.</t>
+          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
+Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
+13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
+Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -3886,14 +3884,14 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>8200000</t>
+          <t>2990000</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
       <c r="Q20" s="1" t="inlineStr"/>
       <c r="R20" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/tverstroymash-993941-0al4980/08.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
         </is>
       </c>
       <c r="S20" s="1" t="inlineStr"/>
@@ -3923,7 +3921,7 @@
       <c r="AA20" s="1" t="inlineStr"/>
       <c r="AB20" s="1" t="inlineStr">
         <is>
-          <t>8200000</t>
+          <t>2990000</t>
         </is>
       </c>
       <c r="AC20" s="1" t="inlineStr">
@@ -3953,12 +3951,12 @@
       </c>
       <c r="AP20" s="1" t="inlineStr">
         <is>
-          <t>Тверьстроймаш</t>
+          <t>V-Trailer</t>
         </is>
       </c>
       <c r="AQ20" s="1" t="inlineStr">
         <is>
-          <t>993941</t>
+          <t>329</t>
         </is>
       </c>
       <c r="AR20" s="1" t="inlineStr">
@@ -3968,24 +3966,24 @@
       </c>
       <c r="AS20" s="1" t="inlineStr">
         <is>
-          <t>Трал (тяжеловоз)</t>
+          <t>Шторный</t>
         </is>
       </c>
       <c r="AT20" s="1" t="inlineStr"/>
       <c r="AU20" s="1" t="inlineStr"/>
       <c r="AV20" s="1" t="inlineStr">
         <is>
-          <t>X89993940R0AL4980</t>
+          <t>XZFVKRP3DR0000119</t>
         </is>
       </c>
       <c r="AW20" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AX20" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY20" s="1" t="inlineStr">
@@ -3995,192 +3993,26 @@
       </c>
       <c r="AZ20" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
+          <t>Дисковые</t>
         </is>
       </c>
       <c r="BA20" s="1" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="BB20" s="1" t="inlineStr">
         <is>
-          <t>10790</t>
-        </is>
-      </c>
-      <c r="BC20" s="1" t="inlineStr"/>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="BC20" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
       <c r="BD20" s="1" t="inlineStr"/>
       <c r="BE20" s="1" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15с2</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr"/>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>v-trailer-329d-r0000119</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr"/>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M21" s="1" t="inlineStr">
-        <is>
-          <t>Шторный полуприцеп V-Trailer 329D, 2023 год, в работе, полностью исправен.
-Оси SAF, подъёмная передняя — меньше износ резины и расход на порожняке. Опорное устройство JOST на 24 тонны, шкворень 2 дюйма по ISO 1726. Пол — влагостойкая фанера 30 мм, держит погрузчик до 7,5 тонн. Крыша сдвижная (Sesam/Edscha) — грузить сверху краном или погрузчиком без снятия тента. Двери алюминиевые BPW Smartmaster II, передний и задний портал — стальные, собственной конструкции. Рама облегчённая, с дополнительными усилениями против скручивания. По бортам — корзины под коники, по 7 штук на сторону.
-13,6 × 2,5 × 4 м, 91 м³. Тент плотный: борта 900 г/м², крыша 680 г/м². Полная штора, без бортов — удобно под европаллеты и груз с выступом по высоте.
-Возможна аренда с правом выкупа — уточняйте условия по телефону.</t>
-        </is>
-      </c>
-      <c r="N21" s="1" t="inlineStr">
-        <is>
-          <t>Грузовики и спецтехника</t>
-        </is>
-      </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>2990000</t>
-        </is>
-      </c>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr"/>
-      <c r="R21" s="1" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-trailers/photos/v-trailer-329d-r0000119/r2-06.jpg</t>
-        </is>
-      </c>
-      <c r="S21" s="1" t="inlineStr"/>
-      <c r="T21" s="1" t="inlineStr"/>
-      <c r="U21" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15с2</t>
-        </is>
-      </c>
-      <c r="V21" s="1" t="inlineStr"/>
-      <c r="W21" s="1" t="inlineStr"/>
-      <c r="X21" s="1" t="inlineStr">
-        <is>
-          <t>Прицепы</t>
-        </is>
-      </c>
-      <c r="Y21" s="1" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="Z21" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AA21" s="1" t="inlineStr"/>
-      <c r="AB21" s="1" t="inlineStr">
-        <is>
-          <t>2990000</t>
-        </is>
-      </c>
-      <c r="AC21" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD21" s="1" t="inlineStr"/>
-      <c r="AE21" s="1" t="inlineStr"/>
-      <c r="AF21" s="1" t="inlineStr"/>
-      <c r="AG21" s="1" t="inlineStr"/>
-      <c r="AH21" s="1" t="inlineStr"/>
-      <c r="AI21" s="1" t="inlineStr"/>
-      <c r="AJ21" s="1" t="inlineStr"/>
-      <c r="AK21" s="1" t="inlineStr"/>
-      <c r="AL21" s="1" t="inlineStr"/>
-      <c r="AM21" s="1" t="inlineStr">
-        <is>
-          <t>С пробегом</t>
-        </is>
-      </c>
-      <c r="AN21" s="1" t="inlineStr"/>
-      <c r="AO21" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AP21" s="1" t="inlineStr">
-        <is>
-          <t>V-Trailer</t>
-        </is>
-      </c>
-      <c r="AQ21" s="1" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="AR21" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AS21" s="1" t="inlineStr">
-        <is>
-          <t>Шторный</t>
-        </is>
-      </c>
-      <c r="AT21" s="1" t="inlineStr"/>
-      <c r="AU21" s="1" t="inlineStr"/>
-      <c r="AV21" s="1" t="inlineStr">
-        <is>
-          <t>XZFVKRP3DR0000119</t>
-        </is>
-      </c>
-      <c r="AW21" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="AX21" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AY21" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
-      <c r="AZ21" s="1" t="inlineStr">
-        <is>
-          <t>Дисковые</t>
-        </is>
-      </c>
-      <c r="BA21" s="1" t="inlineStr">
-        <is>
-          <t>32300</t>
-        </is>
-      </c>
-      <c r="BB21" s="1" t="inlineStr">
-        <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="BC21" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="BD21" s="1" t="inlineStr"/>
-      <c r="BE21" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
